--- a/Sep_2026/daily Reports/Sales Reporting Depricated.xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Depricated.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BF9A8A-6E44-4B30-B984-DE409170C06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8093405A-B447-4700-84B5-109DE0CD8FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1167,60 +1167,60 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1532,55 +1532,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="105" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="108" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="110"/>
+      <c r="G1" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="111" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
+      <c r="V1" s="112"/>
+      <c r="W1" s="113"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46288</v>
-      </c>
-      <c r="G2" s="111" t="s">
+        <v>46289</v>
+      </c>
+      <c r="G2" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="112" t="s">
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="115" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="112"/>
-      <c r="M2" s="113"/>
+      <c r="L2" s="115"/>
+      <c r="M2" s="116"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="111" t="s">
+      <c r="P2" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="112" t="s">
+      <c r="Q2" s="115"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="115" t="s">
         <v>3</v>
       </c>
-      <c r="T2" s="112"/>
-      <c r="U2" s="113"/>
+      <c r="T2" s="115"/>
+      <c r="U2" s="116"/>
       <c r="V2" s="1"/>
       <c r="W2" s="2"/>
     </row>
@@ -1680,52 +1680,54 @@
       <c r="G4" s="30">
         <v>50</v>
       </c>
-      <c r="H4" s="68"/>
-      <c r="I4" s="31">
-        <v>9</v>
+      <c r="H4" s="68">
+        <v>40</v>
+      </c>
+      <c r="I4" s="12">
+        <v>21</v>
       </c>
       <c r="J4" s="32">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="K4" s="30">
         <v>40</v>
       </c>
-      <c r="L4" s="31">
-        <v>14.425000000000001</v>
+      <c r="L4" s="12">
+        <v>11.9</v>
       </c>
       <c r="M4" s="32">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.36062500000000003</v>
+        <v>0.29749999999999999</v>
       </c>
       <c r="N4" s="90">
         <f>IFERROR(L4/I4,0)</f>
-        <v>1.6027777777777779</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="O4" s="33"/>
       <c r="P4" s="30">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q4" s="31">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
-        <v>0.94117647058823528</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="S4" s="30">
-        <v>4</v>
+        <v>14.425000000000001</v>
       </c>
       <c r="T4" s="31">
-        <v>3</v>
+        <v>14.175000000000001</v>
       </c>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
-        <v>0.75</v>
+        <v>0.98266897746967075</v>
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>0.1875</v>
+        <v>1.7718750000000001</v>
       </c>
       <c r="W4" s="33"/>
       <c r="X4" s="34"/>
@@ -1752,52 +1754,52 @@
       <c r="G5" s="11">
         <v>50</v>
       </c>
-      <c r="H5" s="71"/>
-      <c r="I5" s="12">
-        <v>21</v>
-      </c>
+      <c r="H5" s="71">
+        <v>0</v>
+      </c>
+      <c r="I5" s="12"/>
       <c r="J5" s="13">
         <f t="shared" ref="J5:J32" si="0">IFERROR(I5/G5,0)</f>
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="K5" s="11">
         <v>30</v>
       </c>
       <c r="L5" s="12">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M5" s="13">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0.31666666666666665</v>
+        <v>0</v>
       </c>
       <c r="N5" s="11">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>0.45238095238095238</v>
+        <v>0</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q5" s="12">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R5" s="13">
         <f t="shared" ref="R5:R32" si="3">IFERROR(Q5/P5,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="11">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T5" s="12">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>0</v>
+        <v>0.9631578947368421</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>0</v>
+        <v>0.43571428571428572</v>
       </c>
       <c r="W5" s="14"/>
       <c r="X5" s="34"/>
@@ -1824,44 +1826,46 @@
       <c r="G6" s="11">
         <v>50</v>
       </c>
-      <c r="H6" s="71"/>
+      <c r="H6" s="71">
+        <v>40</v>
+      </c>
       <c r="I6" s="12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="K6" s="11">
         <v>25</v>
       </c>
       <c r="L6" s="12">
-        <v>7</v>
+        <v>7.95</v>
       </c>
       <c r="M6" s="13">
         <f t="shared" si="1"/>
-        <v>0.28000000000000003</v>
+        <v>0.318</v>
       </c>
       <c r="N6" s="11">
         <f t="shared" si="2"/>
-        <v>1.4</v>
+        <v>0.99375000000000002</v>
       </c>
       <c r="O6" s="14"/>
       <c r="P6" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q6" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R6" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S6" s="11">
-        <v>2.4500000000000002</v>
+        <v>7</v>
       </c>
       <c r="T6" s="12">
-        <v>2.4500000000000002</v>
+        <v>7</v>
       </c>
       <c r="U6" s="13">
         <f t="shared" si="4"/>
@@ -1869,7 +1873,7 @@
       </c>
       <c r="V6" s="11">
         <f t="shared" si="5"/>
-        <v>0.61250000000000004</v>
+        <v>1.4</v>
       </c>
       <c r="W6" s="14"/>
       <c r="X6" s="34"/>
@@ -1896,52 +1900,54 @@
       <c r="G7" s="11">
         <v>50</v>
       </c>
-      <c r="H7" s="71"/>
+      <c r="H7" s="71">
+        <v>35</v>
+      </c>
       <c r="I7" s="12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K7" s="11">
         <v>30</v>
       </c>
       <c r="L7" s="12">
-        <v>3.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="M7" s="13">
         <f t="shared" si="1"/>
-        <v>0.12000000000000001</v>
+        <v>0.15333333333333332</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" si="2"/>
-        <v>0.72</v>
+        <v>0.65714285714285714</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="11">
         <v>5</v>
       </c>
       <c r="Q7" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S7" s="11">
-        <v>3.375</v>
+        <v>3.6</v>
       </c>
       <c r="T7" s="12">
-        <v>2.7749999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
-        <v>0.82222222222222219</v>
+        <v>1</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>0.69374999999999998</v>
+        <v>0.72</v>
       </c>
       <c r="W7" s="14"/>
       <c r="X7" s="34"/>
@@ -1968,52 +1974,54 @@
       <c r="G8" s="11">
         <v>50</v>
       </c>
-      <c r="H8" s="71"/>
+      <c r="H8" s="71">
+        <v>45</v>
+      </c>
       <c r="I8" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="K8" s="11">
         <v>20</v>
       </c>
       <c r="L8" s="12">
-        <v>4.3</v>
+        <v>8.15</v>
       </c>
       <c r="M8" s="13">
         <f t="shared" si="1"/>
-        <v>0.215</v>
+        <v>0.40750000000000003</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" si="2"/>
-        <v>0.71666666666666667</v>
+        <v>1.01875</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="11">
         <v>6</v>
       </c>
       <c r="Q8" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="S8" s="11">
-        <v>8.6</v>
+        <v>4.3</v>
       </c>
       <c r="T8" s="12">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.79069767441860461</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>1.4333333333333333</v>
+        <v>0.67999999999999994</v>
       </c>
       <c r="W8" s="14"/>
       <c r="X8" s="34"/>
@@ -2040,52 +2048,50 @@
       <c r="G9" s="11">
         <v>50</v>
       </c>
-      <c r="H9" s="71"/>
-      <c r="I9" s="12">
-        <v>1</v>
-      </c>
+      <c r="H9" s="71">
+        <v>10</v>
+      </c>
+      <c r="I9" s="12"/>
       <c r="J9" s="13">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="K9" s="11">
         <v>0</v>
       </c>
-      <c r="L9" s="12">
-        <v>40</v>
-      </c>
+      <c r="L9" s="12"/>
       <c r="M9" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="2"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O9" s="14"/>
       <c r="P9" s="11">
         <v>3</v>
       </c>
       <c r="Q9" s="12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R9" s="13">
         <f t="shared" si="3"/>
-        <v>1.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="S9" s="11">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="T9" s="12">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="U9" s="13">
         <f t="shared" si="4"/>
-        <v>1.2264150943396226</v>
+        <v>0.67796610169491522</v>
       </c>
       <c r="V9" s="11">
         <f t="shared" si="5"/>
-        <v>16.25</v>
+        <v>40</v>
       </c>
       <c r="W9" s="14"/>
       <c r="X9" s="34"/>
@@ -2112,7 +2118,9 @@
       <c r="G10" s="11">
         <v>50</v>
       </c>
-      <c r="H10" s="71"/>
+      <c r="H10" s="71">
+        <v>40</v>
+      </c>
       <c r="I10" s="12"/>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
@@ -2131,21 +2139,29 @@
         <v>0</v>
       </c>
       <c r="O10" s="14"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="12"/>
+      <c r="P10" s="11">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>12</v>
+      </c>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="11"/>
-      <c r="T10" s="12"/>
+        <v>1.5</v>
+      </c>
+      <c r="S10" s="11">
+        <v>8</v>
+      </c>
+      <c r="T10" s="12">
+        <v>12</v>
+      </c>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="14"/>
       <c r="X10" s="34"/>
@@ -2172,7 +2188,9 @@
       <c r="G11" s="11">
         <v>50</v>
       </c>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <v>40</v>
+      </c>
       <c r="I11" s="12"/>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
@@ -2191,21 +2209,29 @@
         <v>0</v>
       </c>
       <c r="O11" s="14"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="12"/>
+      <c r="P11" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>8</v>
+      </c>
       <c r="R11" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="11"/>
-      <c r="T11" s="12"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="S11" s="11">
+        <v>6</v>
+      </c>
+      <c r="T11" s="12">
+        <v>8</v>
+      </c>
       <c r="U11" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="V11" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="14"/>
       <c r="X11" s="34"/>
@@ -2232,7 +2258,9 @@
       <c r="G12" s="11">
         <v>50</v>
       </c>
-      <c r="H12" s="71"/>
+      <c r="H12" s="71">
+        <v>40</v>
+      </c>
       <c r="I12" s="12"/>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
@@ -2251,21 +2279,29 @@
         <v>0</v>
       </c>
       <c r="O12" s="14"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="12"/>
+      <c r="P12" s="11">
+        <v>9</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>7</v>
+      </c>
       <c r="R12" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S12" s="11"/>
-      <c r="T12" s="12"/>
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="S12" s="11">
+        <v>9</v>
+      </c>
+      <c r="T12" s="12">
+        <v>7</v>
+      </c>
       <c r="U12" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="V12" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="14"/>
       <c r="X12" s="34"/>
@@ -2686,26 +2722,26 @@
       <c r="C20" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="99" t="s">
+      <c r="D20" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="100"/>
-      <c r="F20" s="101"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="104"/>
       <c r="G20" s="40">
         <f>SUM(G4:G19)</f>
         <v>450</v>
       </c>
       <c r="H20" s="41">
         <f>SUM(H4:H19)</f>
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>0.10444444444444445</v>
+        <v>9.7777777777777783E-2</v>
       </c>
       <c r="K20" s="40">
         <v>1</v>
@@ -2719,7 +2755,7 @@
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>2.1276595744680851E-2</v>
+        <v>2.2727272727272728E-2</v>
       </c>
       <c r="O20" s="43">
         <f>AVERAGE(O4:O19)</f>
@@ -2727,31 +2763,31 @@
       </c>
       <c r="P20" s="40">
         <f>SUM(P4:P19)</f>
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="Q20" s="41">
         <f>SUM(Q4:Q19)</f>
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0.97142857142857142</v>
+        <v>1</v>
       </c>
       <c r="S20" s="40">
         <f>SUM(S4:S19)</f>
-        <v>71.424999999999997</v>
+        <v>120.82499999999999</v>
       </c>
       <c r="T20" s="41">
         <f>SUM(T4:T19)</f>
-        <v>81.825000000000003</v>
+        <v>104.325</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>1.1456072803640183</v>
+        <v>0.86343885785226582</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>2.4066176470588236</v>
+        <v>1.4489583333333333</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3123,11 +3159,11 @@
       <c r="C26" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="99" t="s">
+      <c r="D26" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="100"/>
-      <c r="F26" s="101"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="104"/>
       <c r="G26" s="40">
         <f>SUM(G21:G25)</f>
         <v>5</v>
@@ -3490,11 +3526,11 @@
       <c r="C31" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="102" t="s">
+      <c r="D31" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="103"/>
-      <c r="F31" s="104"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="107"/>
       <c r="G31" s="40">
         <f>SUM(G27:G30)</f>
         <v>4</v>
@@ -3580,15 +3616,15 @@
       </c>
       <c r="H32" s="21">
         <f t="shared" ref="H32:I32" si="12">+H31+H26+H20</f>
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="I32" s="21">
         <f t="shared" si="12"/>
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>0.10239651416122005</v>
+        <v>9.586056644880174E-2</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3602,7 +3638,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>2.1276595744680851E-2</v>
+        <v>2.2727272727272728E-2</v>
       </c>
       <c r="O32" s="23">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3610,31 +3646,31 @@
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="13">+Q31+Q26+Q20</f>
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>0.97727272727272729</v>
+        <v>1</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>80.424999999999997</v>
+        <v>129.82499999999999</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="14">+T31+T26+T20</f>
-        <v>90.825000000000003</v>
+        <v>113.325</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>1.1293130245570409</v>
+        <v>0.87290583477758532</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>2.1122093023255815</v>
+        <v>1.3990740740740741</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3699,36 +3735,36 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.76923076923076927</v>
+        <v>0.80769230769230771</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="89">
-        <v>46288</v>
-      </c>
-      <c r="G2" s="111" t="s">
+        <v>46289</v>
+      </c>
+      <c r="G2" s="114" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="108" t="s">
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="111" t="s">
         <v>48</v>
       </c>
-      <c r="L2" s="109"/>
-      <c r="M2" s="109"/>
-      <c r="N2" s="109"/>
-      <c r="O2" s="110"/>
-      <c r="P2" s="114" t="s">
+      <c r="L2" s="112"/>
+      <c r="M2" s="112"/>
+      <c r="N2" s="112"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="115"/>
+      <c r="Q2" s="118"/>
     </row>
     <row r="3" spans="1:18" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="25" t="s">
@@ -3802,7 +3838,7 @@
       <c r="E4" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="116" t="s">
+      <c r="F4" s="99" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="30">
@@ -3810,33 +3846,35 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <v>271</v>
+        <f>271+8</f>
+        <v>279</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.45166666666666666</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="K4" s="7">
         <v>550</v>
       </c>
       <c r="L4" s="8">
-        <v>246.75</v>
+        <f>246.75+14</f>
+        <v>260.75</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.44863636363636361</v>
+        <v>0.47409090909090912</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>303.25</v>
+        <v>289.25</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>50.541666666666664</v>
+        <v>57.85</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P12" si="2">L4/I4</f>
-        <v>0.91051660516605171</v>
+        <v>0.93458781362007171</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3865,33 +3903,35 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <v>277</v>
+        <f>277+21</f>
+        <v>298</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J28" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.46166666666666667</v>
+        <v>0.49666666666666665</v>
       </c>
       <c r="K5" s="11">
         <v>450</v>
       </c>
       <c r="L5" s="12">
-        <v>161.80000000000001</v>
+        <f>161.8+9</f>
+        <v>170.8</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M28" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.35955555555555557</v>
+        <v>0.37955555555555559</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>288.2</v>
+        <v>279.2</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>48.033333333333331</v>
+        <v>55.839999999999996</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>0.58411552346570406</v>
+        <v>0.5731543624161074</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -3920,33 +3960,35 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="12">
-        <v>117</v>
+        <f>117+5</f>
+        <v>122</v>
       </c>
       <c r="J6" s="69">
         <f t="shared" si="3"/>
-        <v>0.19500000000000001</v>
+        <v>0.20333333333333334</v>
       </c>
       <c r="K6" s="11">
         <v>550</v>
       </c>
       <c r="L6" s="12">
-        <v>154.52500000000001</v>
+        <f>154.525+7</f>
+        <v>161.52500000000001</v>
       </c>
       <c r="M6" s="70">
         <f t="shared" si="4"/>
-        <v>0.28095454545454546</v>
+        <v>0.29368181818181821</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
-        <v>395.47500000000002</v>
+        <v>388.47500000000002</v>
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>65.912500000000009</v>
+        <v>77.695000000000007</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
-        <v>1.3207264957264957</v>
+        <v>1.3239754098360657</v>
       </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="34"/>
@@ -3975,33 +4017,35 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <v>121</v>
+        <f>121+5</f>
+        <v>126</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.20166666666666666</v>
+        <v>0.21</v>
       </c>
       <c r="K7" s="11">
         <v>400</v>
       </c>
       <c r="L7" s="12">
-        <v>149.75</v>
+        <f>149.75+4</f>
+        <v>153.75</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.37437500000000001</v>
+        <v>0.38437500000000002</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>250.25</v>
+        <v>246.25</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>41.708333333333336</v>
+        <v>49.25</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.2376033057851239</v>
+        <v>1.2202380952380953</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4030,33 +4074,35 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <v>85</v>
+        <f>85+5</f>
+        <v>90</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.14166666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="K8" s="11">
         <v>575</v>
       </c>
       <c r="L8" s="12">
-        <v>91.724999999999994</v>
+        <f>91.725+3</f>
+        <v>94.724999999999994</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.15952173913043477</v>
+        <v>0.16473913043478261</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N28" si="5">K8-L8</f>
-        <v>483.27499999999998</v>
+        <v>480.27499999999998</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O28" si="6">N8/$D$2</f>
-        <v>80.545833333333334</v>
+        <v>96.054999999999993</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.0791176470588235</v>
+        <v>1.0525</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4085,33 +4131,35 @@
       </c>
       <c r="H9" s="71"/>
       <c r="I9" s="12">
-        <v>73</v>
+        <f>73+3</f>
+        <v>76</v>
       </c>
       <c r="J9" s="69">
         <f t="shared" si="3"/>
-        <v>0.36499999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="K9" s="11">
         <v>3000</v>
       </c>
       <c r="L9" s="12">
-        <v>1494.5250000000001</v>
+        <f>1494.525+59</f>
+        <v>1553.5250000000001</v>
       </c>
       <c r="M9" s="70">
         <f t="shared" si="4"/>
-        <v>0.49817500000000003</v>
+        <v>0.51784166666666664</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="5"/>
-        <v>1505.4749999999999</v>
+        <v>1446.4749999999999</v>
       </c>
       <c r="O9" s="14">
         <f t="shared" si="6"/>
-        <v>250.91249999999999</v>
+        <v>289.29499999999996</v>
       </c>
       <c r="P9" s="71">
         <f t="shared" si="2"/>
-        <v>20.472945205479455</v>
+        <v>20.441118421052632</v>
       </c>
       <c r="Q9" s="14"/>
       <c r="R9" s="34"/>
@@ -4162,7 +4210,7 @@
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>46.5</v>
+        <v>55.8</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
@@ -4217,7 +4265,7 @@
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>58.5</v>
+        <v>70.2</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
@@ -4272,7 +4320,7 @@
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>54</v>
+        <v>64.8</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
@@ -4297,7 +4345,7 @@
       <c r="E13" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="117" t="s">
+      <c r="F13" s="100" t="s">
         <v>66</v>
       </c>
       <c r="G13" s="11">
@@ -4349,7 +4397,7 @@
       <c r="E14" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="117" t="s">
+      <c r="F14" s="100" t="s">
         <v>67</v>
       </c>
       <c r="G14" s="11"/>
@@ -4393,7 +4441,7 @@
       <c r="E15" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="118" t="s">
+      <c r="F15" s="101" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="11"/>
@@ -4431,11 +4479,11 @@
       <c r="C16" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="102" t="s">
+      <c r="D16" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="103"/>
-      <c r="F16" s="104"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="107"/>
       <c r="G16" s="40">
         <f>SUM(G4:G13)</f>
         <v>5000</v>
@@ -4446,11 +4494,11 @@
       </c>
       <c r="I16" s="41">
         <f>SUM(I4:I12)</f>
-        <v>1458</v>
+        <v>1505</v>
       </c>
       <c r="J16" s="75">
         <f t="shared" si="3"/>
-        <v>0.29160000000000003</v>
+        <v>0.30099999999999999</v>
       </c>
       <c r="K16" s="76">
         <f>SUM(K4:K15)</f>
@@ -4458,23 +4506,23 @@
       </c>
       <c r="L16" s="77">
         <f>SUM(L4:L15)</f>
-        <v>3095.0750000000003</v>
+        <v>3191.0750000000003</v>
       </c>
       <c r="M16" s="78">
         <f t="shared" si="4"/>
-        <v>0.42543986254295535</v>
+        <v>0.43863573883161516</v>
       </c>
       <c r="N16" s="77">
         <f t="shared" si="5"/>
-        <v>4179.9249999999993</v>
+        <v>4083.9249999999997</v>
       </c>
       <c r="O16" s="79">
         <f t="shared" si="6"/>
-        <v>696.65416666666658</v>
+        <v>816.78499999999997</v>
       </c>
       <c r="P16" s="80">
         <f>L16/I16</f>
-        <v>2.1228223593964337</v>
+        <v>2.1203156146179403</v>
       </c>
       <c r="Q16" s="43" t="e">
         <f>AVERAGE(Q4:Q15)</f>
@@ -4528,7 +4576,7 @@
       </c>
       <c r="O17" s="10">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P17" s="96">
         <f t="shared" ref="P17:P21" si="7">L17/I17</f>
@@ -4583,7 +4631,7 @@
       </c>
       <c r="O18" s="14">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P18" s="71">
         <f t="shared" si="7"/>
@@ -4638,7 +4686,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4693,7 +4741,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4748,7 +4796,7 @@
       </c>
       <c r="O21" s="94">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P21" s="74">
         <f t="shared" si="7"/>
@@ -4769,11 +4817,11 @@
       <c r="C22" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="102" t="s">
+      <c r="D22" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="103"/>
-      <c r="F22" s="104"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="107"/>
       <c r="G22" s="40">
         <f>SUM(G17:G21)</f>
         <v>5</v>
@@ -4806,7 +4854,7 @@
       </c>
       <c r="O22" s="79">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P22" s="80">
         <f>L22/I22</f>
@@ -4864,7 +4912,7 @@
       </c>
       <c r="O23" s="10">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P23" s="96">
         <f t="shared" ref="P23:P26" si="9">L23/I23</f>
@@ -4919,7 +4967,7 @@
       </c>
       <c r="O24" s="14">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P24" s="71">
         <f t="shared" si="9"/>
@@ -4974,7 +5022,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5029,7 +5077,7 @@
       </c>
       <c r="O26" s="94">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P26" s="74">
         <f t="shared" si="9"/>
@@ -5050,11 +5098,11 @@
       <c r="C27" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="102" t="s">
+      <c r="D27" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="103"/>
-      <c r="F27" s="104"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="107"/>
       <c r="G27" s="40">
         <f>SUM(G23:G26)</f>
         <v>4</v>
@@ -5084,7 +5132,7 @@
       </c>
       <c r="O27" s="79">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P27" s="80">
         <f>L27/I27</f>
@@ -5117,11 +5165,11 @@
       </c>
       <c r="I28" s="21">
         <f t="shared" si="11"/>
-        <v>1467</v>
+        <v>1514</v>
       </c>
       <c r="J28" s="83">
         <f t="shared" si="3"/>
-        <v>0.29287282890796568</v>
+        <v>0.30225593930924338</v>
       </c>
       <c r="K28" s="84">
         <v>600</v>
@@ -5139,11 +5187,11 @@
       </c>
       <c r="O28" s="87">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P28" s="88">
         <f>L28/I28</f>
-        <v>0.11881390593047035</v>
+        <v>0.11512549537648614</v>
       </c>
       <c r="Q28" s="23" t="e">
         <f>AVERAGE(Q27,Q16,Q22)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Depricated.xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Depricated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8093405A-B447-4700-84B5-109DE0CD8FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6BD94C-5F4A-4F46-8380-77C7A60C79ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -3735,18 +3735,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.80769230769230771</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" s="89">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>34</v>
@@ -3846,35 +3846,35 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>271+8</f>
-        <v>279</v>
+        <f>271+8+7</f>
+        <v>286</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.46500000000000002</v>
+        <v>0.47666666666666668</v>
       </c>
       <c r="K4" s="7">
         <v>550</v>
       </c>
       <c r="L4" s="8">
-        <f>246.75+14</f>
-        <v>260.75</v>
+        <f>246.75+14+8</f>
+        <v>268.75</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.47409090909090912</v>
+        <v>0.48863636363636365</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>289.25</v>
+        <v>281.25</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>57.85</v>
+        <v>70.3125</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P12" si="2">L4/I4</f>
-        <v>0.93458781362007171</v>
+        <v>0.93968531468531469</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>55.839999999999996</v>
+        <v>69.8</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
@@ -3960,35 +3960,35 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="12">
-        <f>117+5</f>
-        <v>122</v>
+        <f>117+5+5</f>
+        <v>127</v>
       </c>
       <c r="J6" s="69">
         <f t="shared" si="3"/>
-        <v>0.20333333333333334</v>
+        <v>0.21166666666666667</v>
       </c>
       <c r="K6" s="11">
         <v>550</v>
       </c>
       <c r="L6" s="12">
-        <f>154.525+7</f>
-        <v>161.52500000000001</v>
+        <f>154.525+7+19</f>
+        <v>180.52500000000001</v>
       </c>
       <c r="M6" s="70">
         <f t="shared" si="4"/>
-        <v>0.29368181818181821</v>
+        <v>0.32822727272727276</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
-        <v>388.47500000000002</v>
+        <v>369.47500000000002</v>
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>77.695000000000007</v>
+        <v>92.368750000000006</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
-        <v>1.3239754098360657</v>
+        <v>1.4214566929133858</v>
       </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="34"/>
@@ -4017,35 +4017,35 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>121+5</f>
-        <v>126</v>
+        <f>121+5+6</f>
+        <v>132</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="K7" s="11">
         <v>400</v>
       </c>
       <c r="L7" s="12">
-        <f>149.75+4</f>
-        <v>153.75</v>
+        <f>149.75+4+11</f>
+        <v>164.75</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.38437500000000002</v>
+        <v>0.41187499999999999</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>246.25</v>
+        <v>235.25</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>49.25</v>
+        <v>58.8125</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.2202380952380953</v>
+        <v>1.2481060606060606</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4074,35 +4074,35 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>85+5</f>
-        <v>90</v>
+        <f>85+5+5</f>
+        <v>95</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.15</v>
+        <v>0.15833333333333333</v>
       </c>
       <c r="K8" s="11">
         <v>575</v>
       </c>
       <c r="L8" s="12">
-        <f>91.725+3</f>
-        <v>94.724999999999994</v>
+        <f>91.725+3+5</f>
+        <v>99.724999999999994</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.16473913043478261</v>
+        <v>0.17343478260869563</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N28" si="5">K8-L8</f>
-        <v>480.27499999999998</v>
+        <v>475.27499999999998</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O28" si="6">N8/$D$2</f>
-        <v>96.054999999999993</v>
+        <v>118.81874999999999</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.0525</v>
+        <v>1.0497368421052631</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4131,35 +4131,35 @@
       </c>
       <c r="H9" s="71"/>
       <c r="I9" s="12">
-        <f>73+3</f>
-        <v>76</v>
+        <f>73+3+5</f>
+        <v>81</v>
       </c>
       <c r="J9" s="69">
         <f t="shared" si="3"/>
-        <v>0.38</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="K9" s="11">
         <v>3000</v>
       </c>
       <c r="L9" s="12">
-        <f>1494.525+59</f>
-        <v>1553.5250000000001</v>
+        <f>1494.525+59+106</f>
+        <v>1659.5250000000001</v>
       </c>
       <c r="M9" s="70">
         <f t="shared" si="4"/>
-        <v>0.51784166666666664</v>
+        <v>0.55317500000000008</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="5"/>
-        <v>1446.4749999999999</v>
+        <v>1340.4749999999999</v>
       </c>
       <c r="O9" s="14">
         <f t="shared" si="6"/>
-        <v>289.29499999999996</v>
+        <v>335.11874999999998</v>
       </c>
       <c r="P9" s="71">
         <f t="shared" si="2"/>
-        <v>20.441118421052632</v>
+        <v>20.487962962962964</v>
       </c>
       <c r="Q9" s="14"/>
       <c r="R9" s="34"/>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>55.8</v>
+        <v>69.75</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>70.2</v>
+        <v>87.75</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>64.8</v>
+        <v>81</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
@@ -4494,11 +4494,11 @@
       </c>
       <c r="I16" s="41">
         <f>SUM(I4:I12)</f>
-        <v>1505</v>
+        <v>1533</v>
       </c>
       <c r="J16" s="75">
         <f t="shared" si="3"/>
-        <v>0.30099999999999999</v>
+        <v>0.30659999999999998</v>
       </c>
       <c r="K16" s="76">
         <f>SUM(K4:K15)</f>
@@ -4506,23 +4506,23 @@
       </c>
       <c r="L16" s="77">
         <f>SUM(L4:L15)</f>
-        <v>3191.0750000000003</v>
+        <v>3340.0750000000003</v>
       </c>
       <c r="M16" s="78">
         <f t="shared" si="4"/>
-        <v>0.43863573883161516</v>
+        <v>0.45911683848797252</v>
       </c>
       <c r="N16" s="77">
         <f t="shared" si="5"/>
-        <v>4083.9249999999997</v>
+        <v>3934.9249999999997</v>
       </c>
       <c r="O16" s="79">
         <f t="shared" si="6"/>
-        <v>816.78499999999997</v>
+        <v>983.73124999999993</v>
       </c>
       <c r="P16" s="80">
         <f>L16/I16</f>
-        <v>2.1203156146179403</v>
+        <v>2.1787834311806917</v>
       </c>
       <c r="Q16" s="43" t="e">
         <f>AVERAGE(Q4:Q15)</f>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O17" s="10">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>106.425</v>
       </c>
       <c r="P17" s="96">
         <f t="shared" ref="P17:P21" si="7">L17/I17</f>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="O18" s="14">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>106.425</v>
       </c>
       <c r="P18" s="71">
         <f t="shared" si="7"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>106.425</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>106.425</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="O21" s="94">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>106.425</v>
       </c>
       <c r="P21" s="74">
         <f t="shared" si="7"/>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="O22" s="79">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>106.425</v>
       </c>
       <c r="P22" s="80">
         <f>L22/I22</f>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="O23" s="10">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>106.425</v>
       </c>
       <c r="P23" s="96">
         <f t="shared" ref="P23:P26" si="9">L23/I23</f>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="O24" s="14">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>106.425</v>
       </c>
       <c r="P24" s="71">
         <f t="shared" si="9"/>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>106.425</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="O26" s="94">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>106.425</v>
       </c>
       <c r="P26" s="74">
         <f t="shared" si="9"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O27" s="79">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>106.425</v>
       </c>
       <c r="P27" s="80">
         <f>L27/I27</f>
@@ -5165,11 +5165,11 @@
       </c>
       <c r="I28" s="21">
         <f t="shared" si="11"/>
-        <v>1514</v>
+        <v>1542</v>
       </c>
       <c r="J28" s="83">
         <f t="shared" si="3"/>
-        <v>0.30225593930924338</v>
+        <v>0.30784587742064284</v>
       </c>
       <c r="K28" s="84">
         <v>600</v>
@@ -5187,11 +5187,11 @@
       </c>
       <c r="O28" s="87">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>106.425</v>
       </c>
       <c r="P28" s="88">
         <f>L28/I28</f>
-        <v>0.11512549537648614</v>
+        <v>0.11303501945525292</v>
       </c>
       <c r="Q28" s="23" t="e">
         <f>AVERAGE(Q27,Q16,Q22)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Depricated.xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6BD94C-5F4A-4F46-8380-77C7A60C79ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04E1BEF-4CDA-486D-87EA-5F057D48EC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1556,7 +1556,7 @@
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>2</v>
@@ -1684,50 +1684,50 @@
         <v>40</v>
       </c>
       <c r="I4" s="12">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J4" s="32">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.42</v>
+        <v>0.02</v>
       </c>
       <c r="K4" s="30">
         <v>40</v>
       </c>
       <c r="L4" s="12">
-        <v>11.9</v>
+        <v>60</v>
       </c>
       <c r="M4" s="32">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.29749999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="N4" s="90">
         <f>IFERROR(L4/I4,0)</f>
-        <v>0.56666666666666665</v>
+        <v>60</v>
       </c>
       <c r="O4" s="33"/>
       <c r="P4" s="30">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Q4" s="31">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
-        <v>0.88888888888888884</v>
+        <v>1.0476190476190477</v>
       </c>
       <c r="S4" s="30">
-        <v>14.425000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="T4" s="31">
-        <v>14.175000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
-        <v>0.98266897746967075</v>
+        <v>1</v>
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>1.7718750000000001</v>
+        <v>0.54090909090909089</v>
       </c>
       <c r="W4" s="33"/>
       <c r="X4" s="34"/>
@@ -1755,51 +1755,49 @@
         <v>50</v>
       </c>
       <c r="H5" s="71">
-        <v>0</v>
-      </c>
-      <c r="I5" s="12"/>
+        <v>45</v>
+      </c>
+      <c r="I5" s="12">
+        <v>19</v>
+      </c>
       <c r="J5" s="13">
         <f t="shared" ref="J5:J32" si="0">IFERROR(I5/G5,0)</f>
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="K5" s="11">
         <v>30</v>
       </c>
       <c r="L5" s="12">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M5" s="13">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0</v>
+        <v>0.31666666666666665</v>
       </c>
       <c r="N5" s="11">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O5" s="14"/>
-      <c r="P5" s="11">
-        <v>21</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>21</v>
-      </c>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="12"/>
       <c r="R5" s="13">
         <f t="shared" ref="R5:R32" si="3">IFERROR(Q5/P5,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" s="11">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T5" s="12">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>0.9631578947368421</v>
+        <v>0</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>0.43571428571428572</v>
+        <v>0</v>
       </c>
       <c r="W5" s="14"/>
       <c r="X5" s="34"/>
@@ -1830,50 +1828,50 @@
         <v>40</v>
       </c>
       <c r="I6" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="K6" s="11">
         <v>25</v>
       </c>
       <c r="L6" s="12">
-        <v>7.95</v>
+        <v>16.8</v>
       </c>
       <c r="M6" s="13">
         <f t="shared" si="1"/>
-        <v>0.318</v>
+        <v>0.67200000000000004</v>
       </c>
       <c r="N6" s="11">
         <f t="shared" si="2"/>
-        <v>0.99375000000000002</v>
+        <v>1.8666666666666667</v>
       </c>
       <c r="O6" s="14"/>
       <c r="P6" s="11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q6" s="12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R6" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S6" s="11">
-        <v>7</v>
+        <v>7.95</v>
       </c>
       <c r="T6" s="12">
-        <v>7</v>
+        <v>7.45</v>
       </c>
       <c r="U6" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.93710691823899372</v>
       </c>
       <c r="V6" s="11">
         <f t="shared" si="5"/>
-        <v>1.4</v>
+        <v>0.93125000000000002</v>
       </c>
       <c r="W6" s="14"/>
       <c r="X6" s="34"/>
@@ -1901,53 +1899,53 @@
         <v>50</v>
       </c>
       <c r="H7" s="71">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I7" s="12">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="K7" s="11">
         <v>30</v>
       </c>
       <c r="L7" s="12">
-        <v>4.5999999999999996</v>
+        <v>2</v>
       </c>
       <c r="M7" s="13">
         <f t="shared" si="1"/>
-        <v>0.15333333333333332</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" si="2"/>
-        <v>0.65714285714285714</v>
+        <v>2</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q7" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S7" s="11">
-        <v>3.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="T7" s="12">
         <v>3.6</v>
       </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.78260869565217395</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
       <c r="W7" s="14"/>
       <c r="X7" s="34"/>
@@ -1975,53 +1973,53 @@
         <v>50</v>
       </c>
       <c r="H8" s="71">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I8" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="K8" s="11">
         <v>20</v>
       </c>
       <c r="L8" s="12">
-        <v>8.15</v>
+        <v>6.55</v>
       </c>
       <c r="M8" s="13">
         <f t="shared" si="1"/>
-        <v>0.40750000000000003</v>
+        <v>0.32750000000000001</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" si="2"/>
-        <v>1.01875</v>
+        <v>1.6375</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q8" s="12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="S8" s="11">
-        <v>4.3</v>
+        <v>8.15</v>
       </c>
       <c r="T8" s="12">
-        <v>3.4</v>
+        <v>8.85</v>
       </c>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>0.79069767441860461</v>
+        <v>1.0858895705521472</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>0.67999999999999994</v>
+        <v>1.10625</v>
       </c>
       <c r="W8" s="14"/>
       <c r="X8" s="34"/>
@@ -2051,47 +2049,51 @@
       <c r="H9" s="71">
         <v>10</v>
       </c>
-      <c r="I9" s="12"/>
+      <c r="I9" s="12">
+        <v>9</v>
+      </c>
       <c r="J9" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="K9" s="11">
-        <v>0</v>
-      </c>
-      <c r="L9" s="12"/>
+        <v>80</v>
+      </c>
+      <c r="L9" s="12">
+        <v>124</v>
+      </c>
       <c r="M9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>13.777777777777779</v>
       </c>
       <c r="O9" s="14"/>
       <c r="P9" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="12">
         <v>1</v>
       </c>
       <c r="R9" s="13">
         <f t="shared" si="3"/>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="S9" s="11">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="T9" s="12">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="U9" s="13">
         <f t="shared" si="4"/>
-        <v>0.67796610169491522</v>
+        <v>1</v>
       </c>
       <c r="V9" s="11">
         <f t="shared" si="5"/>
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="W9" s="14"/>
       <c r="X9" s="34"/>
@@ -2119,49 +2121,53 @@
         <v>50</v>
       </c>
       <c r="H10" s="71">
-        <v>40</v>
-      </c>
-      <c r="I10" s="12"/>
+        <v>45</v>
+      </c>
+      <c r="I10" s="12">
+        <v>7</v>
+      </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K10" s="11">
-        <v>200</v>
-      </c>
-      <c r="L10" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="L10" s="12">
+        <v>7</v>
+      </c>
       <c r="M10" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="11">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="Q10" s="12">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="S10" s="11">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T10" s="12">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="W10" s="14"/>
       <c r="X10" s="34"/>
@@ -2191,47 +2197,51 @@
       <c r="H11" s="71">
         <v>40</v>
       </c>
-      <c r="I11" s="12"/>
+      <c r="I11" s="12">
+        <v>20</v>
+      </c>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K11" s="11">
         <v>20</v>
       </c>
-      <c r="L11" s="12"/>
+      <c r="L11" s="12">
+        <v>25</v>
+      </c>
       <c r="M11" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="11">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="Q11" s="12">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="R11" s="13">
         <f t="shared" si="3"/>
-        <v>1.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="S11" s="11">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T11" s="12">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="U11" s="13">
         <f t="shared" si="4"/>
-        <v>1.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="V11" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.1764705882352942</v>
       </c>
       <c r="W11" s="14"/>
       <c r="X11" s="34"/>
@@ -2261,7 +2271,9 @@
       <c r="H12" s="71">
         <v>40</v>
       </c>
-      <c r="I12" s="12"/>
+      <c r="I12" s="12">
+        <v>0</v>
+      </c>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2269,7 +2281,9 @@
       <c r="K12" s="11">
         <v>30</v>
       </c>
-      <c r="L12" s="12"/>
+      <c r="L12" s="12">
+        <v>0</v>
+      </c>
       <c r="M12" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2280,24 +2294,24 @@
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="11">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="12">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R12" s="13">
         <f t="shared" si="3"/>
-        <v>0.77777777777777779</v>
+        <v>1</v>
       </c>
       <c r="S12" s="11">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T12" s="12">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U12" s="13">
         <f t="shared" si="4"/>
-        <v>0.77777777777777779</v>
+        <v>1</v>
       </c>
       <c r="V12" s="11">
         <f t="shared" si="5"/>
@@ -2733,29 +2747,31 @@
       </c>
       <c r="H20" s="41">
         <f>SUM(H4:H19)</f>
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>9.7777777777777783E-2</v>
+        <v>0.15555555555555556</v>
       </c>
       <c r="K20" s="40">
-        <v>1</v>
-      </c>
-      <c r="L20" s="41">
-        <v>1</v>
+        <f>SUM(K4:K12)</f>
+        <v>295</v>
+      </c>
+      <c r="L20" s="40">
+        <f>SUM(L4:L12)</f>
+        <v>250.85</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.85033898305084743</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>2.2727272727272728E-2</v>
+        <v>3.5835714285714286</v>
       </c>
       <c r="O20" s="43">
         <f>AVERAGE(O4:O19)</f>
@@ -2763,31 +2779,31 @@
       </c>
       <c r="P20" s="40">
         <f>SUM(P4:P19)</f>
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="41">
         <f>SUM(Q4:Q19)</f>
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.97619047619047616</v>
       </c>
       <c r="S20" s="40">
         <f>SUM(S4:S19)</f>
-        <v>120.82499999999999</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="T20" s="41">
         <f>SUM(T4:T19)</f>
-        <v>104.325</v>
+        <v>76.800000000000011</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0.86343885785226582</v>
+        <v>0.98969072164948479</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>1.4489583333333333</v>
+        <v>0.9365853658536587</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3616,15 +3632,15 @@
       </c>
       <c r="H32" s="21">
         <f t="shared" ref="H32:I32" si="12">+H31+H26+H20</f>
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="I32" s="21">
         <f t="shared" si="12"/>
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>9.586056644880174E-2</v>
+        <v>0.15250544662309368</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3638,7 +3654,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>2.2727272727272728E-2</v>
+        <v>1.4285714285714285E-2</v>
       </c>
       <c r="O32" s="23">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3646,31 +3662,31 @@
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="13">+Q31+Q26+Q20</f>
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.978494623655914</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>129.82499999999999</v>
+        <v>86.6</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="14">+T31+T26+T20</f>
-        <v>113.325</v>
+        <v>85.800000000000011</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.87290583477758532</v>
+        <v>0.99076212471131664</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>1.3990740740740741</v>
+        <v>0.94285714285714295</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3735,18 +3751,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.84615384615384615</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" s="89">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>34</v>
@@ -3846,35 +3862,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>271+8+7</f>
-        <v>286</v>
+        <f>271+8+7+21</f>
+        <v>307</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.47666666666666668</v>
+        <v>0.51166666666666671</v>
       </c>
       <c r="K4" s="7">
         <v>550</v>
       </c>
       <c r="L4" s="8">
-        <f>246.75+14+8</f>
-        <v>268.75</v>
+        <v>281</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.48863636363636365</v>
+        <v>0.51090909090909087</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>281.25</v>
+        <v>269</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>70.3125</v>
+        <v>134.5</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P12" si="2">L4/I4</f>
-        <v>0.93968531468531469</v>
+        <v>0.91530944625407162</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3914,24 +3929,23 @@
         <v>450</v>
       </c>
       <c r="L5" s="12">
-        <f>161.8+9</f>
-        <v>170.8</v>
+        <v>171</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M28" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.37955555555555559</v>
+        <v>0.38</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>279.2</v>
+        <v>279</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>69.8</v>
+        <v>139.5</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>0.5731543624161074</v>
+        <v>0.5738255033557047</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -3960,35 +3974,34 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="12">
-        <f>117+5+5</f>
-        <v>127</v>
+        <f>117+5+5+8</f>
+        <v>135</v>
       </c>
       <c r="J6" s="69">
         <f t="shared" si="3"/>
-        <v>0.21166666666666667</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="K6" s="11">
         <v>550</v>
       </c>
       <c r="L6" s="12">
-        <f>154.525+7+19</f>
-        <v>180.52500000000001</v>
+        <v>187</v>
       </c>
       <c r="M6" s="70">
         <f t="shared" si="4"/>
-        <v>0.32822727272727276</v>
+        <v>0.34</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
-        <v>369.47500000000002</v>
+        <v>363</v>
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>92.368750000000006</v>
+        <v>181.5</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
-        <v>1.4214566929133858</v>
+        <v>1.3851851851851851</v>
       </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="34"/>
@@ -4017,35 +4030,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>121+5+6</f>
-        <v>132</v>
+        <f>121+5+6+4</f>
+        <v>136</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.22</v>
+        <v>0.22666666666666666</v>
       </c>
       <c r="K7" s="11">
         <v>400</v>
       </c>
       <c r="L7" s="12">
-        <f>149.75+4+11</f>
-        <v>164.75</v>
+        <v>168</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.41187499999999999</v>
+        <v>0.42</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>235.25</v>
+        <v>232</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>58.8125</v>
+        <v>116</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.2481060606060606</v>
+        <v>1.2352941176470589</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4074,35 +4086,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>85+5+5</f>
-        <v>95</v>
+        <f>85+5+5+8</f>
+        <v>103</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.15833333333333333</v>
+        <v>0.17166666666666666</v>
       </c>
       <c r="K8" s="11">
         <v>575</v>
       </c>
       <c r="L8" s="12">
-        <f>91.725+3+5</f>
-        <v>99.724999999999994</v>
+        <v>109</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.17343478260869563</v>
+        <v>0.18956521739130436</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N28" si="5">K8-L8</f>
-        <v>475.27499999999998</v>
+        <v>466</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O28" si="6">N8/$D$2</f>
-        <v>118.81874999999999</v>
+        <v>233</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.0497368421052631</v>
+        <v>1.058252427184466</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4131,35 +4142,34 @@
       </c>
       <c r="H9" s="71"/>
       <c r="I9" s="12">
-        <f>73+3+5</f>
-        <v>81</v>
+        <f>73+3+5+1</f>
+        <v>82</v>
       </c>
       <c r="J9" s="69">
         <f t="shared" si="3"/>
-        <v>0.40500000000000003</v>
+        <v>0.41</v>
       </c>
       <c r="K9" s="11">
         <v>3000</v>
       </c>
       <c r="L9" s="12">
-        <f>1494.525+59+106</f>
-        <v>1659.5250000000001</v>
+        <v>1666</v>
       </c>
       <c r="M9" s="70">
         <f t="shared" si="4"/>
-        <v>0.55317500000000008</v>
+        <v>0.55533333333333335</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="5"/>
-        <v>1340.4749999999999</v>
+        <v>1334</v>
       </c>
       <c r="O9" s="14">
         <f t="shared" si="6"/>
-        <v>335.11874999999998</v>
+        <v>667</v>
       </c>
       <c r="P9" s="71">
         <f t="shared" si="2"/>
-        <v>20.487962962962964</v>
+        <v>20.317073170731707</v>
       </c>
       <c r="Q9" s="14"/>
       <c r="R9" s="34"/>
@@ -4188,33 +4198,35 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <v>219</v>
+        <f>219+20</f>
+        <v>239</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.36499999999999999</v>
+        <v>0.39833333333333332</v>
       </c>
       <c r="K10" s="11">
         <v>650</v>
       </c>
       <c r="L10" s="12">
-        <v>371</v>
+        <f>371+7+20</f>
+        <v>398</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.57076923076923081</v>
+        <v>0.61230769230769233</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>69.75</v>
+        <v>126</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>1.6940639269406392</v>
+        <v>1.6652719665271967</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4243,33 +4255,35 @@
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
-        <v>156</v>
+        <f>156+20</f>
+        <v>176</v>
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>0.26</v>
+        <v>0.29333333333333333</v>
       </c>
       <c r="K11" s="11">
         <v>550</v>
       </c>
       <c r="L11" s="12">
-        <v>199</v>
+        <f>199+20</f>
+        <v>219</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.36181818181818182</v>
+        <v>0.39818181818181819</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>87.75</v>
+        <v>165.5</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>1.2756410256410255</v>
+        <v>1.2443181818181819</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="34"/>
@@ -4298,33 +4312,35 @@
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="12">
-        <v>139</v>
+        <f>139+10</f>
+        <v>149</v>
       </c>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>0.23166666666666666</v>
+        <v>0.24833333333333332</v>
       </c>
       <c r="K12" s="11">
         <v>450</v>
       </c>
       <c r="L12" s="12">
-        <v>126</v>
+        <f>126+2</f>
+        <v>128</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.28000000000000003</v>
+        <v>0.28444444444444444</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>0.90647482014388492</v>
+        <v>0.85906040268456374</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="34"/>
@@ -4494,11 +4510,11 @@
       </c>
       <c r="I16" s="41">
         <f>SUM(I4:I12)</f>
-        <v>1533</v>
+        <v>1625</v>
       </c>
       <c r="J16" s="75">
         <f t="shared" si="3"/>
-        <v>0.30659999999999998</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="K16" s="76">
         <f>SUM(K4:K15)</f>
@@ -4506,23 +4522,23 @@
       </c>
       <c r="L16" s="77">
         <f>SUM(L4:L15)</f>
-        <v>3340.0750000000003</v>
+        <v>3427</v>
       </c>
       <c r="M16" s="78">
         <f t="shared" si="4"/>
-        <v>0.45911683848797252</v>
+        <v>0.47106529209621995</v>
       </c>
       <c r="N16" s="77">
         <f t="shared" si="5"/>
-        <v>3934.9249999999997</v>
+        <v>3848</v>
       </c>
       <c r="O16" s="79">
         <f t="shared" si="6"/>
-        <v>983.73124999999993</v>
+        <v>1924</v>
       </c>
       <c r="P16" s="80">
         <f>L16/I16</f>
-        <v>2.1787834311806917</v>
+        <v>2.1089230769230771</v>
       </c>
       <c r="Q16" s="43" t="e">
         <f>AVERAGE(Q4:Q15)</f>
@@ -4576,7 +4592,7 @@
       </c>
       <c r="O17" s="10">
         <f t="shared" si="6"/>
-        <v>106.425</v>
+        <v>212.85</v>
       </c>
       <c r="P17" s="96">
         <f t="shared" ref="P17:P21" si="7">L17/I17</f>
@@ -4631,7 +4647,7 @@
       </c>
       <c r="O18" s="14">
         <f t="shared" si="6"/>
-        <v>106.425</v>
+        <v>212.85</v>
       </c>
       <c r="P18" s="71">
         <f t="shared" si="7"/>
@@ -4686,7 +4702,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>106.425</v>
+        <v>212.85</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4741,7 +4757,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>106.425</v>
+        <v>212.85</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4796,7 +4812,7 @@
       </c>
       <c r="O21" s="94">
         <f t="shared" si="6"/>
-        <v>106.425</v>
+        <v>212.85</v>
       </c>
       <c r="P21" s="74">
         <f t="shared" si="7"/>
@@ -4854,7 +4870,7 @@
       </c>
       <c r="O22" s="79">
         <f t="shared" si="6"/>
-        <v>106.425</v>
+        <v>212.85</v>
       </c>
       <c r="P22" s="80">
         <f>L22/I22</f>
@@ -4912,7 +4928,7 @@
       </c>
       <c r="O23" s="10">
         <f t="shared" si="6"/>
-        <v>106.425</v>
+        <v>212.85</v>
       </c>
       <c r="P23" s="96">
         <f t="shared" ref="P23:P26" si="9">L23/I23</f>
@@ -4967,7 +4983,7 @@
       </c>
       <c r="O24" s="14">
         <f t="shared" si="6"/>
-        <v>106.425</v>
+        <v>212.85</v>
       </c>
       <c r="P24" s="71">
         <f t="shared" si="9"/>
@@ -5022,7 +5038,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>106.425</v>
+        <v>212.85</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5077,7 +5093,7 @@
       </c>
       <c r="O26" s="94">
         <f t="shared" si="6"/>
-        <v>106.425</v>
+        <v>212.85</v>
       </c>
       <c r="P26" s="74">
         <f t="shared" si="9"/>
@@ -5132,7 +5148,7 @@
       </c>
       <c r="O27" s="79">
         <f t="shared" si="6"/>
-        <v>106.425</v>
+        <v>212.85</v>
       </c>
       <c r="P27" s="80">
         <f>L27/I27</f>
@@ -5165,11 +5181,11 @@
       </c>
       <c r="I28" s="21">
         <f t="shared" si="11"/>
-        <v>1542</v>
+        <v>1634</v>
       </c>
       <c r="J28" s="83">
         <f t="shared" si="3"/>
-        <v>0.30784587742064284</v>
+        <v>0.32621281692952686</v>
       </c>
       <c r="K28" s="84">
         <v>600</v>
@@ -5187,11 +5203,11 @@
       </c>
       <c r="O28" s="87">
         <f t="shared" si="6"/>
-        <v>106.425</v>
+        <v>212.85</v>
       </c>
       <c r="P28" s="88">
         <f>L28/I28</f>
-        <v>0.11303501945525292</v>
+        <v>0.10667074663402694</v>
       </c>
       <c r="Q28" s="23" t="e">
         <f>AVERAGE(Q27,Q16,Q22)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Depricated.xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Depricated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04E1BEF-4CDA-486D-87EA-5F057D48EC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B840CC2-5C5B-4B00-B0EB-09E0CB0A90C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -1684,50 +1684,46 @@
         <v>40</v>
       </c>
       <c r="I4" s="12">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J4" s="32">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
       <c r="K4" s="30">
         <v>40</v>
       </c>
       <c r="L4" s="12">
-        <v>60</v>
+        <v>10.5</v>
       </c>
       <c r="M4" s="32">
         <f>IFERROR(L4/K4,0)</f>
-        <v>1.5</v>
+        <v>0.26250000000000001</v>
       </c>
       <c r="N4" s="90">
         <f>IFERROR(L4/I4,0)</f>
-        <v>60</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="O4" s="33"/>
       <c r="P4" s="30">
         <v>21</v>
       </c>
-      <c r="Q4" s="31">
-        <v>22</v>
-      </c>
+      <c r="Q4" s="31"/>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
-        <v>1.0476190476190477</v>
+        <v>0</v>
       </c>
       <c r="S4" s="30">
         <v>11.9</v>
       </c>
-      <c r="T4" s="31">
-        <v>11.9</v>
-      </c>
+      <c r="T4" s="31"/>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>0.54090909090909089</v>
+        <v>0</v>
       </c>
       <c r="W4" s="33"/>
       <c r="X4" s="34"/>
@@ -1758,25 +1754,25 @@
         <v>45</v>
       </c>
       <c r="I5" s="12">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" ref="J5:J32" si="0">IFERROR(I5/G5,0)</f>
-        <v>0.38</v>
+        <v>0.54</v>
       </c>
       <c r="K5" s="11">
         <v>30</v>
       </c>
       <c r="L5" s="12">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="M5" s="13">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0.31666666666666665</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N5" s="11">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>0.5</v>
+        <v>0.37037037037037035</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="11"/>
@@ -1788,9 +1784,7 @@
       <c r="S5" s="11">
         <v>0</v>
       </c>
-      <c r="T5" s="12">
-        <v>0</v>
-      </c>
+      <c r="T5" s="12"/>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
         <v>0</v>
@@ -1828,50 +1822,46 @@
         <v>40</v>
       </c>
       <c r="I6" s="12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K6" s="11">
         <v>25</v>
       </c>
       <c r="L6" s="12">
-        <v>16.8</v>
+        <v>15.25</v>
       </c>
       <c r="M6" s="13">
         <f t="shared" si="1"/>
-        <v>0.67200000000000004</v>
+        <v>0.61</v>
       </c>
       <c r="N6" s="11">
         <f t="shared" si="2"/>
-        <v>1.8666666666666667</v>
+        <v>2.1785714285714284</v>
       </c>
       <c r="O6" s="14"/>
       <c r="P6" s="11">
         <v>8</v>
       </c>
-      <c r="Q6" s="12">
-        <v>8</v>
-      </c>
+      <c r="Q6" s="12"/>
       <c r="R6" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" s="11">
         <v>7.95</v>
       </c>
-      <c r="T6" s="12">
-        <v>7.45</v>
-      </c>
+      <c r="T6" s="12"/>
       <c r="U6" s="13">
         <f t="shared" si="4"/>
-        <v>0.93710691823899372</v>
+        <v>0</v>
       </c>
       <c r="V6" s="11">
         <f t="shared" si="5"/>
-        <v>0.93125000000000002</v>
+        <v>0</v>
       </c>
       <c r="W6" s="14"/>
       <c r="X6" s="34"/>
@@ -1902,50 +1892,46 @@
         <v>45</v>
       </c>
       <c r="I7" s="12">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
       <c r="K7" s="11">
         <v>30</v>
       </c>
       <c r="L7" s="12">
-        <v>2</v>
+        <v>10.1</v>
       </c>
       <c r="M7" s="13">
         <f t="shared" si="1"/>
-        <v>6.6666666666666666E-2</v>
+        <v>0.33666666666666667</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1.1222222222222222</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="11">
         <v>7</v>
       </c>
-      <c r="Q7" s="12">
-        <v>4</v>
-      </c>
+      <c r="Q7" s="12"/>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="S7" s="11">
         <v>4.5999999999999996</v>
       </c>
-      <c r="T7" s="12">
-        <v>3.6</v>
-      </c>
+      <c r="T7" s="12"/>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
-        <v>0.78260869565217395</v>
+        <v>0</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="W7" s="14"/>
       <c r="X7" s="34"/>
@@ -1976,50 +1962,46 @@
         <v>40</v>
       </c>
       <c r="I8" s="12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="K8" s="11">
         <v>20</v>
       </c>
       <c r="L8" s="12">
-        <v>6.55</v>
+        <v>7.25</v>
       </c>
       <c r="M8" s="13">
         <f t="shared" si="1"/>
-        <v>0.32750000000000001</v>
+        <v>0.36249999999999999</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" si="2"/>
-        <v>1.6375</v>
+        <v>1.2083333333333333</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="11">
         <v>8</v>
       </c>
-      <c r="Q8" s="12">
-        <v>8</v>
-      </c>
+      <c r="Q8" s="12"/>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" s="11">
         <v>8.15</v>
       </c>
-      <c r="T8" s="12">
-        <v>8.85</v>
-      </c>
+      <c r="T8" s="12"/>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>1.0858895705521472</v>
+        <v>0</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>1.10625</v>
+        <v>0</v>
       </c>
       <c r="W8" s="14"/>
       <c r="X8" s="34"/>
@@ -2050,50 +2032,46 @@
         <v>10</v>
       </c>
       <c r="I9" s="12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J9" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="K9" s="11">
         <v>80</v>
       </c>
       <c r="L9" s="12">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="M9" s="13">
         <f t="shared" si="1"/>
-        <v>1.55</v>
+        <v>1.3625</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="2"/>
-        <v>13.777777777777779</v>
+        <v>18.166666666666668</v>
       </c>
       <c r="O9" s="14"/>
       <c r="P9" s="11">
         <v>1</v>
       </c>
-      <c r="Q9" s="12">
-        <v>1</v>
-      </c>
+      <c r="Q9" s="12"/>
       <c r="R9" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" s="11">
         <v>6</v>
       </c>
-      <c r="T9" s="12">
-        <v>6</v>
-      </c>
+      <c r="T9" s="12"/>
       <c r="U9" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="11">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W9" s="14"/>
       <c r="X9" s="34"/>
@@ -2123,51 +2101,43 @@
       <c r="H10" s="71">
         <v>45</v>
       </c>
-      <c r="I10" s="12">
-        <v>7</v>
-      </c>
+      <c r="I10" s="12"/>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
       <c r="K10" s="11">
         <v>20</v>
       </c>
-      <c r="L10" s="12">
-        <v>7</v>
-      </c>
+      <c r="L10" s="12"/>
       <c r="M10" s="13">
         <f t="shared" si="1"/>
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="11">
         <v>20</v>
       </c>
-      <c r="Q10" s="12">
-        <v>20</v>
-      </c>
+      <c r="Q10" s="12"/>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" s="11">
         <v>17</v>
       </c>
-      <c r="T10" s="12">
-        <v>17</v>
-      </c>
+      <c r="T10" s="12"/>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="W10" s="14"/>
       <c r="X10" s="34"/>
@@ -2197,51 +2167,43 @@
       <c r="H11" s="71">
         <v>40</v>
       </c>
-      <c r="I11" s="12">
-        <v>20</v>
-      </c>
+      <c r="I11" s="12"/>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K11" s="11">
         <v>20</v>
       </c>
-      <c r="L11" s="12">
-        <v>25</v>
-      </c>
+      <c r="L11" s="12"/>
       <c r="M11" s="13">
         <f t="shared" si="1"/>
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="2"/>
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="11">
         <v>17</v>
       </c>
-      <c r="Q11" s="12">
-        <v>17</v>
-      </c>
+      <c r="Q11" s="12"/>
       <c r="R11" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="11">
         <v>20</v>
       </c>
-      <c r="T11" s="12">
-        <v>20</v>
-      </c>
+      <c r="T11" s="12"/>
       <c r="U11" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="11">
         <f t="shared" si="5"/>
-        <v>1.1764705882352942</v>
+        <v>0</v>
       </c>
       <c r="W11" s="14"/>
       <c r="X11" s="34"/>
@@ -2271,9 +2233,7 @@
       <c r="H12" s="71">
         <v>40</v>
       </c>
-      <c r="I12" s="12">
-        <v>0</v>
-      </c>
+      <c r="I12" s="12"/>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2281,9 +2241,7 @@
       <c r="K12" s="11">
         <v>30</v>
       </c>
-      <c r="L12" s="12">
-        <v>0</v>
-      </c>
+      <c r="L12" s="12"/>
       <c r="M12" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2296,26 +2254,22 @@
       <c r="P12" s="11">
         <v>2</v>
       </c>
-      <c r="Q12" s="12">
-        <v>2</v>
-      </c>
+      <c r="Q12" s="12"/>
       <c r="R12" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="11">
         <v>2</v>
       </c>
-      <c r="T12" s="12">
-        <v>2</v>
-      </c>
+      <c r="T12" s="12"/>
       <c r="U12" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" s="14"/>
       <c r="X12" s="34"/>
@@ -2751,11 +2705,11 @@
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>0.15555555555555556</v>
+        <v>0.14222222222222222</v>
       </c>
       <c r="K20" s="40">
         <f>SUM(K4:K12)</f>
@@ -2763,15 +2717,15 @@
       </c>
       <c r="L20" s="40">
         <f>SUM(L4:L12)</f>
-        <v>250.85</v>
+        <v>162.1</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.85033898305084743</v>
+        <v>0.54949152542372881</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>3.5835714285714286</v>
+        <v>2.5328124999999999</v>
       </c>
       <c r="O20" s="43">
         <f>AVERAGE(O4:O19)</f>
@@ -2783,11 +2737,11 @@
       </c>
       <c r="Q20" s="41">
         <f>SUM(Q4:Q19)</f>
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0.97619047619047616</v>
+        <v>0</v>
       </c>
       <c r="S20" s="40">
         <f>SUM(S4:S19)</f>
@@ -2795,15 +2749,15 @@
       </c>
       <c r="T20" s="41">
         <f>SUM(T4:T19)</f>
-        <v>76.800000000000011</v>
+        <v>0</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0.98969072164948479</v>
+        <v>0</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>0.9365853658536587</v>
+        <v>0</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3636,11 +3590,11 @@
       </c>
       <c r="I32" s="21">
         <f t="shared" si="12"/>
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>0.15250544662309368</v>
+        <v>0.13943355119825709</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3654,7 +3608,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>1.4285714285714285E-2</v>
+        <v>1.5625E-2</v>
       </c>
       <c r="O32" s="23">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3666,11 +3620,11 @@
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="13">+Q31+Q26+Q20</f>
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>0.978494623655914</v>
+        <v>9.6774193548387094E-2</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
@@ -3678,15 +3632,15 @@
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="14">+T31+T26+T20</f>
-        <v>85.800000000000011</v>
+        <v>9</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.99076212471131664</v>
+        <v>0.10392609699769054</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>0.94285714285714295</v>
+        <v>1</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Depricated.xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Depricated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B840CC2-5C5B-4B00-B0EB-09E0CB0A90C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD5D0B9-EA9E-4F6E-B253-9211352E095C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -1556,7 +1556,7 @@
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>2</v>
@@ -1706,24 +1706,28 @@
       </c>
       <c r="O4" s="33"/>
       <c r="P4" s="30">
-        <v>21</v>
-      </c>
-      <c r="Q4" s="31"/>
+        <v>1</v>
+      </c>
+      <c r="Q4" s="31">
+        <v>1</v>
+      </c>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" s="30">
-        <v>11.9</v>
-      </c>
-      <c r="T4" s="31"/>
+        <v>60</v>
+      </c>
+      <c r="T4" s="31">
+        <v>60</v>
+      </c>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="W4" s="33"/>
       <c r="X4" s="34"/>
@@ -1775,23 +1779,29 @@
         <v>0.37037037037037035</v>
       </c>
       <c r="O5" s="14"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="12"/>
+      <c r="P5" s="11">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>18</v>
+      </c>
       <c r="R5" s="13">
         <f t="shared" ref="R5:R32" si="3">IFERROR(Q5/P5,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="11">
-        <v>0</v>
-      </c>
-      <c r="T5" s="12"/>
+        <v>9.5</v>
+      </c>
+      <c r="T5" s="12">
+        <v>8</v>
+      </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>0</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>0</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="W5" s="14"/>
       <c r="X5" s="34"/>
@@ -1846,22 +1856,26 @@
       <c r="P6" s="11">
         <v>8</v>
       </c>
-      <c r="Q6" s="12"/>
+      <c r="Q6" s="12">
+        <v>8</v>
+      </c>
       <c r="R6" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="11">
-        <v>7.95</v>
-      </c>
-      <c r="T6" s="12"/>
+        <v>16.8</v>
+      </c>
+      <c r="T6" s="12">
+        <v>14.8</v>
+      </c>
       <c r="U6" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.88095238095238093</v>
       </c>
       <c r="V6" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W6" s="14"/>
       <c r="X6" s="34"/>
@@ -1914,7 +1928,7 @@
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="11">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="12"/>
       <c r="R7" s="13">
@@ -1922,9 +1936,11 @@
         <v>0</v>
       </c>
       <c r="S7" s="11">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="T7" s="12"/>
+        <v>2</v>
+      </c>
+      <c r="T7" s="12">
+        <v>0</v>
+      </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -1984,24 +2000,28 @@
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="11">
-        <v>8</v>
-      </c>
-      <c r="Q8" s="12"/>
+        <v>3</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>3</v>
+      </c>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="11">
-        <v>8.15</v>
-      </c>
-      <c r="T8" s="12"/>
+        <v>6.55</v>
+      </c>
+      <c r="T8" s="12">
+        <v>5.65</v>
+      </c>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.86259541984732835</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1.8833333333333335</v>
       </c>
       <c r="W8" s="14"/>
       <c r="X8" s="34"/>
@@ -2054,24 +2074,28 @@
       </c>
       <c r="O9" s="14"/>
       <c r="P9" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>7</v>
+      </c>
       <c r="R9" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="11">
-        <v>6</v>
-      </c>
-      <c r="T9" s="12"/>
+        <v>124</v>
+      </c>
+      <c r="T9" s="12">
+        <v>100.5</v>
+      </c>
       <c r="U9" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.81048387096774188</v>
       </c>
       <c r="V9" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>14.357142857142858</v>
       </c>
       <c r="W9" s="14"/>
       <c r="X9" s="34"/>
@@ -2101,43 +2125,51 @@
       <c r="H10" s="71">
         <v>45</v>
       </c>
-      <c r="I10" s="12"/>
+      <c r="I10" s="12">
+        <v>10</v>
+      </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K10" s="11">
         <v>20</v>
       </c>
-      <c r="L10" s="12"/>
+      <c r="L10" s="12">
+        <v>12</v>
+      </c>
       <c r="M10" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="11">
-        <v>20</v>
-      </c>
-      <c r="Q10" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>7</v>
+      </c>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="11">
-        <v>17</v>
-      </c>
-      <c r="T10" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="T10" s="12">
+        <v>7</v>
+      </c>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="14"/>
       <c r="X10" s="34"/>
@@ -2167,43 +2199,51 @@
       <c r="H11" s="71">
         <v>40</v>
       </c>
-      <c r="I11" s="12"/>
+      <c r="I11" s="12">
+        <v>7</v>
+      </c>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K11" s="11">
         <v>20</v>
       </c>
-      <c r="L11" s="12"/>
+      <c r="L11" s="12">
+        <v>10</v>
+      </c>
       <c r="M11" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.4285714285714286</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="11">
-        <v>17</v>
-      </c>
-      <c r="Q11" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>20</v>
+      </c>
       <c r="R11" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="11">
-        <v>20</v>
-      </c>
-      <c r="T11" s="12"/>
+        <v>25</v>
+      </c>
+      <c r="T11" s="12">
+        <v>25</v>
+      </c>
       <c r="U11" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11" s="14"/>
       <c r="X11" s="34"/>
@@ -2233,36 +2273,44 @@
       <c r="H12" s="71">
         <v>40</v>
       </c>
-      <c r="I12" s="12"/>
+      <c r="I12" s="12">
+        <v>18</v>
+      </c>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="K12" s="11">
         <v>30</v>
       </c>
-      <c r="L12" s="12"/>
+      <c r="L12" s="12">
+        <v>9</v>
+      </c>
       <c r="M12" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0</v>
+      </c>
       <c r="R12" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S12" s="11">
-        <v>2</v>
-      </c>
-      <c r="T12" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="12">
+        <v>0</v>
+      </c>
       <c r="U12" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -2705,11 +2753,11 @@
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>0.14222222222222222</v>
+        <v>0.22</v>
       </c>
       <c r="K20" s="40">
         <f>SUM(K4:K12)</f>
@@ -2717,15 +2765,15 @@
       </c>
       <c r="L20" s="40">
         <f>SUM(L4:L12)</f>
-        <v>162.1</v>
+        <v>193.1</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.54949152542372881</v>
+        <v>0.65457627118644068</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>2.5328124999999999</v>
+        <v>1.9505050505050505</v>
       </c>
       <c r="O20" s="43">
         <f>AVERAGE(O4:O19)</f>
@@ -2733,31 +2781,31 @@
       </c>
       <c r="P20" s="40">
         <f>SUM(P4:P19)</f>
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="Q20" s="41">
         <f>SUM(Q4:Q19)</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.98461538461538467</v>
       </c>
       <c r="S20" s="40">
         <f>SUM(S4:S19)</f>
-        <v>77.599999999999994</v>
+        <v>250.85</v>
       </c>
       <c r="T20" s="41">
         <f>SUM(T4:T19)</f>
-        <v>0</v>
+        <v>220.95</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.88080526210882992</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.4523437499999998</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3590,11 +3638,11 @@
       </c>
       <c r="I32" s="21">
         <f t="shared" si="12"/>
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>0.13943355119825709</v>
+        <v>0.21568627450980393</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3608,7 +3656,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>1.5625E-2</v>
+        <v>1.0101010101010102E-2</v>
       </c>
       <c r="O32" s="23">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3616,31 +3664,31 @@
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="13">+Q31+Q26+Q20</f>
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>9.6774193548387094E-2</v>
+        <v>0.98648648648648651</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>86.6</v>
+        <v>259.85000000000002</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="14">+T31+T26+T20</f>
-        <v>9</v>
+        <v>229.95</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.10392609699769054</v>
+        <v>0.88493361554743111</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>3.15</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3705,18 +3753,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.92307692307692313</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="89">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>34</v>
@@ -3816,34 +3864,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>271+8+7+21</f>
-        <v>307</v>
+        <f>271+8+7+21+1+8</f>
+        <v>316</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.51166666666666671</v>
+        <v>0.52666666666666662</v>
       </c>
       <c r="K4" s="7">
         <v>550</v>
       </c>
       <c r="L4" s="8">
-        <v>281</v>
+        <v>349.77499999999998</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.51090909090909087</v>
+        <v>0.63595454545454544</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>269</v>
+        <v>200.22500000000002</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>134.5</v>
+        <v>200.22500000000002</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P12" si="2">L4/I4</f>
-        <v>0.91530944625407162</v>
+        <v>1.106882911392405</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3872,34 +3920,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>277+21</f>
-        <v>298</v>
+        <f>277+21+18+15</f>
+        <v>331</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J28" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.49666666666666665</v>
+        <v>0.55166666666666664</v>
       </c>
       <c r="K5" s="11">
         <v>450</v>
       </c>
       <c r="L5" s="12">
-        <v>171</v>
+        <v>188.95</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M28" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.38</v>
+        <v>0.41988888888888887</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>279</v>
+        <v>261.05</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>139.5</v>
+        <v>261.05</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>0.5738255033557047</v>
+        <v>0.57084592145015101</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -3928,34 +3976,34 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="12">
-        <f>117+5+5+8</f>
-        <v>135</v>
+        <f>117+5+5+8+8+5</f>
+        <v>148</v>
       </c>
       <c r="J6" s="69">
         <f t="shared" si="3"/>
-        <v>0.22500000000000001</v>
+        <v>0.24666666666666667</v>
       </c>
       <c r="K6" s="11">
         <v>550</v>
       </c>
       <c r="L6" s="12">
-        <v>187</v>
+        <v>211.22499999999999</v>
       </c>
       <c r="M6" s="70">
         <f t="shared" si="4"/>
-        <v>0.34</v>
+        <v>0.38404545454545452</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
-        <v>363</v>
+        <v>338.77499999999998</v>
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>181.5</v>
+        <v>338.77499999999998</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
-        <v>1.3851851851851851</v>
+        <v>1.427195945945946</v>
       </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="34"/>
@@ -3984,34 +4032,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>121+5+6+4</f>
-        <v>136</v>
+        <f>121+5+6+4+8</f>
+        <v>144</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.22666666666666666</v>
+        <v>0.24</v>
       </c>
       <c r="K7" s="11">
         <v>400</v>
       </c>
       <c r="L7" s="12">
-        <v>168</v>
+        <v>176.4</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.42</v>
+        <v>0.441</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>232</v>
+        <v>223.6</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>116</v>
+        <v>223.6</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.2352941176470589</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4040,34 +4088,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>85+5+5+8</f>
-        <v>103</v>
+        <f>85+5+5+8+3+2</f>
+        <v>108</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.17166666666666666</v>
+        <v>0.18</v>
       </c>
       <c r="K8" s="11">
         <v>575</v>
       </c>
       <c r="L8" s="12">
-        <v>109</v>
+        <v>120.77500000000001</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.18956521739130436</v>
+        <v>0.21004347826086958</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N28" si="5">K8-L8</f>
-        <v>466</v>
+        <v>454.22500000000002</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O28" si="6">N8/$D$2</f>
-        <v>233</v>
+        <v>454.22500000000002</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.058252427184466</v>
+        <v>1.118287037037037</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4096,34 +4144,34 @@
       </c>
       <c r="H9" s="71"/>
       <c r="I9" s="12">
-        <f>73+3+5+1</f>
-        <v>82</v>
+        <f>73+3+5+1+7+5</f>
+        <v>94</v>
       </c>
       <c r="J9" s="69">
         <f t="shared" si="3"/>
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="K9" s="11">
         <v>3000</v>
       </c>
       <c r="L9" s="12">
-        <v>1666</v>
+        <v>1876.925</v>
       </c>
       <c r="M9" s="70">
         <f t="shared" si="4"/>
-        <v>0.55533333333333335</v>
+        <v>0.62564166666666665</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="5"/>
-        <v>1334</v>
+        <v>1123.075</v>
       </c>
       <c r="O9" s="14">
         <f t="shared" si="6"/>
-        <v>667</v>
+        <v>1123.075</v>
       </c>
       <c r="P9" s="71">
         <f t="shared" si="2"/>
-        <v>20.317073170731707</v>
+        <v>19.967287234042551</v>
       </c>
       <c r="Q9" s="14"/>
       <c r="R9" s="34"/>
@@ -4152,35 +4200,35 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>219+20</f>
-        <v>239</v>
+        <f>219+20+7</f>
+        <v>246</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.39833333333333332</v>
+        <v>0.41</v>
       </c>
       <c r="K10" s="11">
         <v>650</v>
       </c>
       <c r="L10" s="12">
-        <f>371+7+20</f>
-        <v>398</v>
+        <f>371+7+20+7</f>
+        <v>405</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.61230769230769233</v>
+        <v>0.62307692307692308</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>126</v>
+        <v>245</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>1.6652719665271967</v>
+        <v>1.6463414634146341</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4209,35 +4257,35 @@
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
-        <f>156+20</f>
-        <v>176</v>
+        <f>156+20+20</f>
+        <v>196</v>
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>0.29333333333333333</v>
+        <v>0.32666666666666666</v>
       </c>
       <c r="K11" s="11">
         <v>550</v>
       </c>
       <c r="L11" s="12">
-        <f>199+20</f>
-        <v>219</v>
+        <f>199+20+25</f>
+        <v>244</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.39818181818181819</v>
+        <v>0.44363636363636366</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>165.5</v>
+        <v>306</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>1.2443181818181819</v>
+        <v>1.2448979591836735</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="34"/>
@@ -4290,7 +4338,7 @@
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>161</v>
+        <v>322</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
@@ -4464,11 +4512,11 @@
       </c>
       <c r="I16" s="41">
         <f>SUM(I4:I12)</f>
-        <v>1625</v>
+        <v>1732</v>
       </c>
       <c r="J16" s="75">
         <f t="shared" si="3"/>
-        <v>0.32500000000000001</v>
+        <v>0.34639999999999999</v>
       </c>
       <c r="K16" s="76">
         <f>SUM(K4:K15)</f>
@@ -4476,23 +4524,23 @@
       </c>
       <c r="L16" s="77">
         <f>SUM(L4:L15)</f>
-        <v>3427</v>
+        <v>3801.05</v>
       </c>
       <c r="M16" s="78">
         <f t="shared" si="4"/>
-        <v>0.47106529209621995</v>
+        <v>0.52248109965635736</v>
       </c>
       <c r="N16" s="77">
         <f t="shared" si="5"/>
-        <v>3848</v>
+        <v>3473.95</v>
       </c>
       <c r="O16" s="79">
         <f t="shared" si="6"/>
-        <v>1924</v>
+        <v>3473.95</v>
       </c>
       <c r="P16" s="80">
         <f>L16/I16</f>
-        <v>2.1089230769230771</v>
+        <v>2.1946016166281757</v>
       </c>
       <c r="Q16" s="43" t="e">
         <f>AVERAGE(Q4:Q15)</f>
@@ -4546,7 +4594,7 @@
       </c>
       <c r="O17" s="10">
         <f t="shared" si="6"/>
-        <v>212.85</v>
+        <v>425.7</v>
       </c>
       <c r="P17" s="96">
         <f t="shared" ref="P17:P21" si="7">L17/I17</f>
@@ -4601,7 +4649,7 @@
       </c>
       <c r="O18" s="14">
         <f t="shared" si="6"/>
-        <v>212.85</v>
+        <v>425.7</v>
       </c>
       <c r="P18" s="71">
         <f t="shared" si="7"/>
@@ -4656,7 +4704,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>212.85</v>
+        <v>425.7</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4711,7 +4759,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>212.85</v>
+        <v>425.7</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4766,7 +4814,7 @@
       </c>
       <c r="O21" s="94">
         <f t="shared" si="6"/>
-        <v>212.85</v>
+        <v>425.7</v>
       </c>
       <c r="P21" s="74">
         <f t="shared" si="7"/>
@@ -4824,7 +4872,7 @@
       </c>
       <c r="O22" s="79">
         <f t="shared" si="6"/>
-        <v>212.85</v>
+        <v>425.7</v>
       </c>
       <c r="P22" s="80">
         <f>L22/I22</f>
@@ -4882,7 +4930,7 @@
       </c>
       <c r="O23" s="10">
         <f t="shared" si="6"/>
-        <v>212.85</v>
+        <v>425.7</v>
       </c>
       <c r="P23" s="96">
         <f t="shared" ref="P23:P26" si="9">L23/I23</f>
@@ -4937,7 +4985,7 @@
       </c>
       <c r="O24" s="14">
         <f t="shared" si="6"/>
-        <v>212.85</v>
+        <v>425.7</v>
       </c>
       <c r="P24" s="71">
         <f t="shared" si="9"/>
@@ -4992,7 +5040,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>212.85</v>
+        <v>425.7</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5047,7 +5095,7 @@
       </c>
       <c r="O26" s="94">
         <f t="shared" si="6"/>
-        <v>212.85</v>
+        <v>425.7</v>
       </c>
       <c r="P26" s="74">
         <f t="shared" si="9"/>
@@ -5102,7 +5150,7 @@
       </c>
       <c r="O27" s="79">
         <f t="shared" si="6"/>
-        <v>212.85</v>
+        <v>425.7</v>
       </c>
       <c r="P27" s="80">
         <f>L27/I27</f>
@@ -5135,11 +5183,11 @@
       </c>
       <c r="I28" s="21">
         <f t="shared" si="11"/>
-        <v>1634</v>
+        <v>1741</v>
       </c>
       <c r="J28" s="83">
         <f t="shared" si="3"/>
-        <v>0.32621281692952686</v>
+        <v>0.34757436614094628</v>
       </c>
       <c r="K28" s="84">
         <v>600</v>
@@ -5157,11 +5205,11 @@
       </c>
       <c r="O28" s="87">
         <f t="shared" si="6"/>
-        <v>212.85</v>
+        <v>425.7</v>
       </c>
       <c r="P28" s="88">
         <f>L28/I28</f>
-        <v>0.10667074663402694</v>
+        <v>0.10011487650775418</v>
       </c>
       <c r="Q28" s="23" t="e">
         <f>AVERAGE(Q27,Q16,Q22)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Depricated.xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Depricated.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB06CFC-3BAB-4478-AA7B-43D6A8569CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E72F06-F1F9-4E3F-AE2B-6B1134A1D4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
-    <sheet name="Till Todate Performance" sheetId="2" r:id="rId2"/>
+    <sheet name="Chart1" sheetId="3" r:id="rId1"/>
+    <sheet name="Today Performance" sheetId="1" r:id="rId2"/>
+    <sheet name="Till Todate Performance" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -242,7 +243,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,6 +297,14 @@
       <color rgb="FFFF0000"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -905,7 +914,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1221,6 +1230,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1237,6 +1250,6596 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Booking</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$G$2:$G$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$H$2:$H$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0">
+                  <c:v>345</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$I$2:$I$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0">
+                  <c:v>82</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$J$2:$J$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0%">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0%">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0%">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0%">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0%">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0%">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0%">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0%">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0%">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0%">
+                  <c:v>0.18222222222222223</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$K$2:$K$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0">
+                  <c:v>295</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$L$2:$L$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0">
+                  <c:v>9.375</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0">
+                  <c:v>6.3</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0">
+                  <c:v>5.7750000000000004</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0">
+                  <c:v>67.5</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0">
+                  <c:v>140.44999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$M$2:$M$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0%">
+                  <c:v>0.234375</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0%">
+                  <c:v>0.36666666666666664</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0%">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0%">
+                  <c:v>0.21</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0%">
+                  <c:v>0.28875000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0%">
+                  <c:v>0.84375</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0%">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0%">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0%">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0%">
+                  <c:v>0.47610169491525423</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$N$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$N$2:$N$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0">
+                  <c:v>1.5625</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0">
+                  <c:v>1.575</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0">
+                  <c:v>0.96250000000000002</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0">
+                  <c:v>6.1363636363636367</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0">
+                  <c:v>1.4285714285714286</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0">
+                  <c:v>1.7128048780487803</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$O$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$O$2:$O$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$P$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Execution</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$P$2:$P$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0">
+                  <c:v>37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$Q$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$Q$2:$Q$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0">
+                  <c:v>31</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$R$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$R$2:$R$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0%">
+                  <c:v>0.88888888888888884</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0%">
+                  <c:v>0.66666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0%">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0%">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0%">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0%">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0%">
+                  <c:v>0.83783783783783783</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="12"/>
+          <c:order val="12"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$S$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$S$2:$S$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.6500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.1749999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>86.5</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0">
+                  <c:v>119.72499999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="13"/>
+          <c:order val="13"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$T$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$T$2:$T$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0">
+                  <c:v>4.6500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0">
+                  <c:v>2.1749999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0">
+                  <c:v>61.325000000000003</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0">
+                  <c:v>90.55</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000D-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="14"/>
+          <c:order val="14"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$U$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$U$2:$U$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0%">
+                  <c:v>0.88235294117647056</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0%">
+                  <c:v>0.8571428571428571</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0%">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0%">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0%">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0%">
+                  <c:v>0.70895953757225438</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0%">
+                  <c:v>0.66666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0%">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0%">
+                  <c:v>0.75631655878053872</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000E-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="15"/>
+          <c:order val="15"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$V$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$V$2:$V$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0">
+                  <c:v>0.9375</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0">
+                  <c:v>0.66428571428571437</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0">
+                  <c:v>1.6333333333333335</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0">
+                  <c:v>0.54374999999999996</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0">
+                  <c:v>0.5714285714285714</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0">
+                  <c:v>2.9209677419354838</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000F-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="16"/>
+          <c:order val="16"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$W$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$W$2:$W$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000010-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="17"/>
+          <c:order val="17"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Today Performance'!$X$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Today Performance'!$A$2:$F$20</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Thursday, October 1, 2026</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>OB Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Zeeshan Maharban</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Salman Butt</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Umair </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jabbar</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Furqan</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Shakoor LMT</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aqeel Malik (SD)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Qasim Khan </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Yasir</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kasoor</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Nabeel Traders </c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Distribution Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Elite Marketing</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>TSO Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>VACANT </c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Total</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>ASM Name</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Rana Bilal</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Area</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="1">
+                    <c:v>Region</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lahore</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Today Performance'!$X$2:$X$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000011-1264-413F-B3BD-6EAA516A62AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="811380767"/>
+        <c:axId val="811393247"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="811380767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="811393247"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="811393247"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="811380767"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{9A2E9A3D-8F3B-4118-8699-A5013BC97B79}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8657167" cy="6286500"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8868091-6CFA-4ADA-57D5-E5D38B789849}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1556,7 +8159,7 @@
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>2</v>
@@ -1684,50 +8287,50 @@
         <v>40</v>
       </c>
       <c r="I4" s="12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J4" s="32">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="K4" s="30">
         <v>40</v>
       </c>
       <c r="L4" s="12">
-        <v>10.5</v>
+        <v>9.375</v>
       </c>
       <c r="M4" s="32">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.26250000000000001</v>
+        <v>0.234375</v>
       </c>
       <c r="N4" s="90">
         <f>IFERROR(L4/I4,0)</f>
-        <v>1.1666666666666667</v>
+        <v>1.5625</v>
       </c>
       <c r="O4" s="33"/>
-      <c r="P4" s="30">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="31">
-        <v>1</v>
+      <c r="P4" s="119">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="119">
+        <v>8</v>
       </c>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
-        <v>1</v>
-      </c>
-      <c r="S4" s="30">
-        <v>60</v>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="S4" s="120">
+        <v>8.5</v>
       </c>
       <c r="T4" s="31">
-        <v>60</v>
+        <v>7.5</v>
       </c>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
-        <v>1</v>
+        <v>0.88235294117647056</v>
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>60</v>
+        <v>0.9375</v>
       </c>
       <c r="W4" s="33"/>
       <c r="X4" s="34"/>
@@ -1758,50 +8361,50 @@
         <v>45</v>
       </c>
       <c r="I5" s="12">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" ref="J5:J32" si="0">IFERROR(I5/G5,0)</f>
-        <v>0.54</v>
+        <v>0.1</v>
       </c>
       <c r="K5" s="11">
         <v>30</v>
       </c>
       <c r="L5" s="12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M5" s="13">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0.33333333333333331</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="N5" s="11">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>0.37037037037037035</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="O5" s="14"/>
-      <c r="P5" s="11">
-        <v>18</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>18</v>
+      <c r="P5" s="119">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="119">
+        <v>2</v>
       </c>
       <c r="R5" s="13">
         <f t="shared" ref="R5:R32" si="3">IFERROR(Q5/P5,0)</f>
-        <v>1</v>
-      </c>
-      <c r="S5" s="11">
-        <v>9.5</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="S5" s="120">
+        <v>7</v>
       </c>
       <c r="T5" s="12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>0.84210526315789469</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>0.44444444444444442</v>
+        <v>3</v>
       </c>
       <c r="W5" s="14"/>
       <c r="X5" s="34"/>
@@ -1832,50 +8435,50 @@
         <v>40</v>
       </c>
       <c r="I6" s="12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="K6" s="11">
         <v>25</v>
       </c>
       <c r="L6" s="12">
-        <v>15.25</v>
+        <v>6.5</v>
       </c>
       <c r="M6" s="13">
         <f t="shared" si="1"/>
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="N6" s="11">
         <f t="shared" si="2"/>
-        <v>2.1785714285714284</v>
+        <v>1.3</v>
       </c>
       <c r="O6" s="14"/>
-      <c r="P6" s="11">
-        <v>8</v>
-      </c>
-      <c r="Q6" s="12">
-        <v>8</v>
+      <c r="P6" s="119">
+        <v>7</v>
+      </c>
+      <c r="Q6" s="119">
+        <v>7</v>
       </c>
       <c r="R6" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="S6" s="11">
-        <v>16.8</v>
+      <c r="S6" s="120">
+        <v>4.6500000000000004</v>
       </c>
       <c r="T6" s="12">
-        <v>14.8</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="U6" s="13">
         <f t="shared" si="4"/>
-        <v>0.88095238095238093</v>
+        <v>1</v>
       </c>
       <c r="V6" s="11">
         <f t="shared" si="5"/>
-        <v>1.85</v>
+        <v>0.66428571428571437</v>
       </c>
       <c r="W6" s="14"/>
       <c r="X6" s="34"/>
@@ -1906,48 +8509,50 @@
         <v>45</v>
       </c>
       <c r="I7" s="12">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="K7" s="11">
         <v>30</v>
       </c>
       <c r="L7" s="12">
-        <v>10.1</v>
+        <v>6.3</v>
       </c>
       <c r="M7" s="13">
         <f t="shared" si="1"/>
-        <v>0.33666666666666667</v>
+        <v>0.21</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" si="2"/>
-        <v>1.1222222222222222</v>
+        <v>1.575</v>
       </c>
       <c r="O7" s="14"/>
-      <c r="P7" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="12"/>
+      <c r="P7" s="119">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="119">
+        <v>3</v>
+      </c>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S7" s="11">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="S7" s="120">
+        <v>4.9000000000000004</v>
       </c>
       <c r="T7" s="12">
-        <v>0</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1.6333333333333335</v>
       </c>
       <c r="W7" s="14"/>
       <c r="X7" s="34"/>
@@ -1988,40 +8593,40 @@
         <v>20</v>
       </c>
       <c r="L8" s="12">
-        <v>7.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="M8" s="13">
         <f t="shared" si="1"/>
-        <v>0.36249999999999999</v>
+        <v>0.28875000000000001</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" si="2"/>
-        <v>1.2083333333333333</v>
+        <v>0.96250000000000002</v>
       </c>
       <c r="O8" s="14"/>
-      <c r="P8" s="11">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="12">
-        <v>3</v>
+      <c r="P8" s="119">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="119">
+        <v>4</v>
       </c>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="S8" s="11">
-        <v>6.55</v>
+      <c r="S8" s="120">
+        <v>2.1749999999999998</v>
       </c>
       <c r="T8" s="12">
-        <v>5.65</v>
+        <v>2.1749999999999998</v>
       </c>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>0.86259541984732835</v>
+        <v>1</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>1.8833333333333335</v>
+        <v>0.54374999999999996</v>
       </c>
       <c r="W8" s="14"/>
       <c r="X8" s="34"/>
@@ -2052,50 +8657,48 @@
         <v>10</v>
       </c>
       <c r="I9" s="12">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J9" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="K9" s="11">
         <v>80</v>
       </c>
       <c r="L9" s="12">
-        <v>109</v>
+        <v>67.5</v>
       </c>
       <c r="M9" s="13">
         <f t="shared" si="1"/>
-        <v>1.3625</v>
+        <v>0.84375</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="2"/>
-        <v>18.166666666666668</v>
+        <v>6.1363636363636367</v>
       </c>
       <c r="O9" s="14"/>
-      <c r="P9" s="11">
-        <v>7</v>
-      </c>
-      <c r="Q9" s="12">
-        <v>7</v>
-      </c>
+      <c r="P9" s="119">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="119"/>
       <c r="R9" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S9" s="11">
-        <v>124</v>
+        <v>0</v>
+      </c>
+      <c r="S9" s="120">
+        <v>86.5</v>
       </c>
       <c r="T9" s="12">
-        <v>100.5</v>
+        <v>61.325000000000003</v>
       </c>
       <c r="U9" s="13">
         <f t="shared" si="4"/>
-        <v>0.81048387096774188</v>
+        <v>0.70895953757225438</v>
       </c>
       <c r="V9" s="11">
         <f t="shared" si="5"/>
-        <v>14.357142857142858</v>
+        <v>0</v>
       </c>
       <c r="W9" s="14"/>
       <c r="X9" s="34"/>
@@ -2126,50 +8729,50 @@
         <v>45</v>
       </c>
       <c r="I10" s="12">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="K10" s="11">
         <v>20</v>
       </c>
       <c r="L10" s="12">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M10" s="13">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="2"/>
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q10" s="12">
         <v>7</v>
       </c>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="S10" s="11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T10" s="12">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W10" s="14"/>
       <c r="X10" s="34"/>
@@ -2222,28 +8825,28 @@
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="11">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="12">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R11" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T11" s="12">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="U11" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="11">
         <f t="shared" si="5"/>
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W11" s="14"/>
       <c r="X11" s="34"/>
@@ -2753,11 +9356,11 @@
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0.18222222222222223</v>
       </c>
       <c r="K20" s="40">
         <f>SUM(K4:K12)</f>
@@ -2765,15 +9368,15 @@
       </c>
       <c r="L20" s="40">
         <f>SUM(L4:L12)</f>
-        <v>193.1</v>
+        <v>140.44999999999999</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.65457627118644068</v>
+        <v>0.47610169491525423</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>1.9505050505050505</v>
+        <v>1.7128048780487803</v>
       </c>
       <c r="O20" s="43">
         <f>AVERAGE(O4:O19)</f>
@@ -2781,31 +9384,31 @@
       </c>
       <c r="P20" s="40">
         <f>SUM(P4:P19)</f>
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Q20" s="41">
         <f>SUM(Q4:Q19)</f>
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0.98461538461538467</v>
+        <v>0.83783783783783783</v>
       </c>
       <c r="S20" s="40">
         <f>SUM(S4:S19)</f>
-        <v>250.85</v>
+        <v>119.72499999999999</v>
       </c>
       <c r="T20" s="41">
         <f>SUM(T4:T19)</f>
-        <v>220.95</v>
+        <v>90.55</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0.88080526210882992</v>
+        <v>0.75631655878053872</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>3.4523437499999998</v>
+        <v>2.9209677419354838</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3638,11 +10241,11 @@
       </c>
       <c r="I32" s="21">
         <f t="shared" si="12"/>
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>0.21568627450980393</v>
+        <v>0.1786492374727669</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3656,7 +10259,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>1.0101010101010102E-2</v>
+        <v>1.2195121951219513E-2</v>
       </c>
       <c r="O32" s="23">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3664,31 +10267,31 @@
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="13">+Q31+Q26+Q20</f>
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>0.98648648648648651</v>
+        <v>0.86956521739130432</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>259.85000000000002</v>
+        <v>128.72499999999999</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="14">+T31+T26+T20</f>
-        <v>229.95</v>
+        <v>99.55</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.88493361554743111</v>
+        <v>0.77335404932996699</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>3.15</v>
+        <v>2.48875</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3864,26 +10467,25 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>271+8+7+21+1+8+16</f>
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.55333333333333334</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="K4" s="7">
         <v>550</v>
       </c>
       <c r="L4" s="8">
-        <v>353.52499999999998</v>
+        <v>354</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.64277272727272727</v>
+        <v>0.64363636363636367</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>196.47500000000002</v>
+        <v>196</v>
       </c>
       <c r="O4" s="10" t="e">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
@@ -3891,7 +10493,7 @@
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P12" si="2">L4/I4</f>
-        <v>1.0648343373493976</v>
+        <v>1.0630630630630631</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3920,26 +10522,25 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>277+21+18+15+30</f>
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J28" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.60166666666666668</v>
+        <v>0.60333333333333339</v>
       </c>
       <c r="K5" s="11">
         <v>450</v>
       </c>
       <c r="L5" s="12">
-        <v>205.95</v>
+        <v>267</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M28" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.45766666666666667</v>
+        <v>0.59333333333333338</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>244.05</v>
+        <v>183</v>
       </c>
       <c r="O5" s="14" t="e">
         <f t="shared" si="1"/>
@@ -3947,7 +10548,7 @@
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>0.57049861495844867</v>
+        <v>0.73756906077348061</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -3976,7 +10577,6 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="12">
-        <f>117+5+5+8+8+5+2</f>
         <v>150</v>
       </c>
       <c r="J6" s="69">
@@ -3987,15 +10587,15 @@
         <v>550</v>
       </c>
       <c r="L6" s="12">
-        <v>212.72499999999999</v>
+        <v>212</v>
       </c>
       <c r="M6" s="70">
         <f t="shared" si="4"/>
-        <v>0.38677272727272727</v>
+        <v>0.38545454545454544</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
-        <v>337.27499999999998</v>
+        <v>338</v>
       </c>
       <c r="O6" s="14" t="e">
         <f t="shared" si="1"/>
@@ -4003,7 +10603,7 @@
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
-        <v>1.4181666666666666</v>
+        <v>1.4133333333333333</v>
       </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="34"/>
@@ -4032,26 +10632,25 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>121+5+6+4+8+2</f>
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.24333333333333335</v>
+        <v>0.24166666666666667</v>
       </c>
       <c r="K7" s="11">
         <v>400</v>
       </c>
       <c r="L7" s="12">
-        <v>180.4</v>
+        <v>180</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.45100000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>219.6</v>
+        <v>220</v>
       </c>
       <c r="O7" s="14" t="e">
         <f t="shared" si="1"/>
@@ -4059,7 +10658,7 @@
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.2356164383561645</v>
+        <v>1.2413793103448276</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4088,26 +10687,25 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>85+5+5+8+3+2+5</f>
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.18833333333333332</v>
+        <v>0.19833333333333333</v>
       </c>
       <c r="K8" s="11">
         <v>575</v>
       </c>
       <c r="L8" s="12">
-        <v>126.65</v>
+        <v>133</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.2202608695652174</v>
+        <v>0.23130434782608697</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N28" si="5">K8-L8</f>
-        <v>448.35</v>
+        <v>442</v>
       </c>
       <c r="O8" s="14" t="e">
         <f t="shared" ref="O8:O28" si="6">N8/$D$2</f>
@@ -4115,7 +10713,7 @@
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.1207964601769913</v>
+        <v>1.1176470588235294</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4144,26 +10742,25 @@
       </c>
       <c r="H9" s="71"/>
       <c r="I9" s="12">
-        <f>73+3+5+1+7+5+4</f>
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="J9" s="69">
         <f t="shared" si="3"/>
-        <v>0.49</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="K9" s="11">
         <v>3000</v>
       </c>
       <c r="L9" s="12">
-        <v>1940.925</v>
+        <v>1921</v>
       </c>
       <c r="M9" s="70">
         <f t="shared" si="4"/>
-        <v>0.64697499999999997</v>
+        <v>0.64033333333333331</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="5"/>
-        <v>1059.075</v>
+        <v>1079</v>
       </c>
       <c r="O9" s="14" t="e">
         <f t="shared" si="6"/>
@@ -4171,7 +10768,7 @@
       </c>
       <c r="P9" s="71">
         <f t="shared" si="2"/>
-        <v>19.805357142857144</v>
+        <v>16.704347826086956</v>
       </c>
       <c r="Q9" s="14"/>
       <c r="R9" s="34"/>
@@ -4199,36 +10796,30 @@
         <v>600</v>
       </c>
       <c r="H10" s="71"/>
-      <c r="I10" s="12">
-        <f>219+20+7</f>
-        <v>246</v>
-      </c>
+      <c r="I10" s="12"/>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="K10" s="11">
         <v>650</v>
       </c>
-      <c r="L10" s="12">
-        <f>371+7+20+7</f>
-        <v>405</v>
-      </c>
+      <c r="L10" s="12"/>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.62307692307692308</v>
+        <v>0</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>245</v>
+        <v>650</v>
       </c>
       <c r="O10" s="14" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P10" s="71">
+      <c r="P10" s="71" t="e">
         <f t="shared" si="2"/>
-        <v>1.6463414634146341</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4256,36 +10847,30 @@
         <v>600</v>
       </c>
       <c r="H11" s="71"/>
-      <c r="I11" s="12">
-        <f>156+20+20</f>
-        <v>196</v>
-      </c>
+      <c r="I11" s="12"/>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>0.32666666666666666</v>
+        <v>0</v>
       </c>
       <c r="K11" s="11">
         <v>550</v>
       </c>
-      <c r="L11" s="12">
-        <f>199+20+25</f>
-        <v>244</v>
-      </c>
+      <c r="L11" s="12"/>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.44363636363636366</v>
+        <v>0</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>306</v>
+        <v>550</v>
       </c>
       <c r="O11" s="14" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P11" s="71">
+      <c r="P11" s="71" t="e">
         <f t="shared" si="2"/>
-        <v>1.2448979591836735</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="34"/>
@@ -4313,36 +10898,30 @@
         <v>600</v>
       </c>
       <c r="H12" s="71"/>
-      <c r="I12" s="12">
-        <f>139+10</f>
-        <v>149</v>
-      </c>
+      <c r="I12" s="12"/>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>0.24833333333333332</v>
+        <v>0</v>
       </c>
       <c r="K12" s="11">
         <v>450</v>
       </c>
-      <c r="L12" s="12">
-        <f>126+2</f>
-        <v>128</v>
-      </c>
+      <c r="L12" s="12"/>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.28444444444444444</v>
+        <v>0</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>322</v>
+        <v>450</v>
       </c>
       <c r="O12" s="14" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P12" s="71">
+      <c r="P12" s="71" t="e">
         <f t="shared" si="2"/>
-        <v>0.85906040268456374</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="34"/>
@@ -4512,11 +11091,11 @@
       </c>
       <c r="I16" s="41">
         <f>SUM(I4:I12)</f>
-        <v>1791</v>
+        <v>1224</v>
       </c>
       <c r="J16" s="75">
         <f t="shared" si="3"/>
-        <v>0.35820000000000002</v>
+        <v>0.24479999999999999</v>
       </c>
       <c r="K16" s="76">
         <f>SUM(K4:K15)</f>
@@ -4524,15 +11103,15 @@
       </c>
       <c r="L16" s="77">
         <f>SUM(L4:L15)</f>
-        <v>3897.1750000000002</v>
+        <v>3167</v>
       </c>
       <c r="M16" s="78">
         <f t="shared" si="4"/>
-        <v>0.53569415807560139</v>
+        <v>0.43532646048109963</v>
       </c>
       <c r="N16" s="77">
         <f t="shared" si="5"/>
-        <v>3377.8249999999998</v>
+        <v>4108</v>
       </c>
       <c r="O16" s="79" t="e">
         <f t="shared" si="6"/>
@@ -4540,7 +11119,7 @@
       </c>
       <c r="P16" s="80">
         <f>L16/I16</f>
-        <v>2.1759771077610273</v>
+        <v>2.5874183006535949</v>
       </c>
       <c r="Q16" s="43" t="e">
         <f>AVERAGE(Q4:Q15)</f>
@@ -5183,11 +11762,11 @@
       </c>
       <c r="I28" s="21">
         <f t="shared" si="11"/>
-        <v>1800</v>
+        <v>1233</v>
       </c>
       <c r="J28" s="83">
         <f t="shared" si="3"/>
-        <v>0.35935316430425235</v>
+        <v>0.24615691754841285</v>
       </c>
       <c r="K28" s="84">
         <v>600</v>
@@ -5209,7 +11788,7 @@
       </c>
       <c r="P28" s="88">
         <f>L28/I28</f>
-        <v>9.6833333333333341E-2</v>
+        <v>0.14136253041362531</v>
       </c>
       <c r="Q28" s="23" t="e">
         <f>AVERAGE(Q27,Q16,Q22)</f>
